--- a/public/data/@Liste GROUPE B-3.xlsx
+++ b/public/data/@Liste GROUPE B-3.xlsx
@@ -410,10 +410,10 @@
     <t>TITINGUERA</t>
   </si>
   <si>
-    <t>MIKE OSCAR</t>
-  </si>
-  <si>
-    <t>ILOUD</t>
+    <t>LÉO EMILIEN</t>
+  </si>
+  <si>
+    <t>NKOA</t>
   </si>
   <si>
     <t>ESPOIR</t>
@@ -1568,10 +1568,10 @@
     <t>NOM DU CAPITAINE : Moustapha Donzo</t>
   </si>
   <si>
-    <t>STÉPHANE LOIC</t>
-  </si>
-  <si>
-    <t>BARBE</t>
+    <t>KOUROUMA NEMA</t>
+  </si>
+  <si>
+    <t>SOUA</t>
   </si>
   <si>
     <t>Guinéen</t>
@@ -2056,7 +2056,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="129">
+  <cellXfs count="130">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -2145,6 +2145,9 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="4" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="5" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -2989,7 +2992,7 @@
       <c r="H3" s="13"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="117" t="s">
+      <c r="A4" s="118" t="s">
         <v>508</v>
       </c>
       <c r="B4" s="5"/>
@@ -3023,10 +3026,10 @@
       <c r="H6" s="13"/>
     </row>
     <row r="7" ht="21.0" customHeight="1">
-      <c r="A7" s="38" t="s">
+      <c r="A7" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="38" t="s">
+      <c r="B7" s="39" t="s">
         <v>51</v>
       </c>
       <c r="C7" s="20" t="s">
@@ -3076,25 +3079,25 @@
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="74">
+      <c r="A8" s="75">
         <v>1.0</v>
       </c>
-      <c r="B8" s="75" t="s">
+      <c r="B8" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="C8" s="41" t="s">
+      <c r="C8" s="42" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="118" t="s">
+      <c r="D8" s="119" t="s">
         <v>510</v>
       </c>
-      <c r="E8" s="118" t="s">
+      <c r="E8" s="119" t="s">
         <v>511</v>
       </c>
-      <c r="F8" s="40">
+      <c r="F8" s="41">
         <v>26.0</v>
       </c>
-      <c r="G8" s="41" t="s">
+      <c r="G8" s="42" t="s">
         <v>512</v>
       </c>
       <c r="H8" s="28"/>
@@ -3112,25 +3115,25 @@
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="76">
+      <c r="A9" s="77">
         <v>2.0</v>
       </c>
-      <c r="B9" s="75" t="s">
+      <c r="B9" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="C9" s="41" t="s">
+      <c r="C9" s="42" t="s">
         <v>86</v>
       </c>
-      <c r="D9" s="75" t="s">
+      <c r="D9" s="76" t="s">
         <v>142</v>
       </c>
-      <c r="E9" s="75" t="s">
+      <c r="E9" s="76" t="s">
         <v>513</v>
       </c>
-      <c r="F9" s="119">
+      <c r="F9" s="120">
         <v>22.0</v>
       </c>
-      <c r="G9" s="120" t="s">
+      <c r="G9" s="121" t="s">
         <v>514</v>
       </c>
       <c r="H9" s="31"/>
@@ -3148,7 +3151,7 @@
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="74">
+      <c r="A10" s="75">
         <v>3.0</v>
       </c>
       <c r="B10" s="3" t="s">
@@ -3157,16 +3160,16 @@
       <c r="C10" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D10" s="75" t="s">
+      <c r="D10" s="76" t="s">
         <v>515</v>
       </c>
-      <c r="E10" s="75" t="s">
+      <c r="E10" s="76" t="s">
         <v>516</v>
       </c>
-      <c r="F10" s="119">
+      <c r="F10" s="120">
         <v>30.0</v>
       </c>
-      <c r="G10" s="120" t="s">
+      <c r="G10" s="121" t="s">
         <v>517</v>
       </c>
       <c r="H10" s="28"/>
@@ -3184,25 +3187,25 @@
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="74">
+      <c r="A11" s="75">
         <v>4.0</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C11" s="120" t="s">
+      <c r="C11" s="121" t="s">
         <v>76</v>
       </c>
-      <c r="D11" s="75" t="s">
+      <c r="D11" s="76" t="s">
         <v>518</v>
       </c>
-      <c r="E11" s="75" t="s">
+      <c r="E11" s="76" t="s">
         <v>519</v>
       </c>
-      <c r="F11" s="119">
+      <c r="F11" s="120">
         <v>25.0</v>
       </c>
-      <c r="G11" s="120" t="s">
+      <c r="G11" s="121" t="s">
         <v>520</v>
       </c>
       <c r="H11" s="28"/>
@@ -3220,23 +3223,23 @@
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="74">
+      <c r="A12" s="75">
         <v>5.0</v>
       </c>
-      <c r="B12" s="75" t="s">
+      <c r="B12" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="120" t="s">
+      <c r="C12" s="121" t="s">
         <v>76</v>
       </c>
-      <c r="D12" s="75" t="s">
+      <c r="D12" s="76" t="s">
         <v>521</v>
       </c>
-      <c r="E12" s="75" t="s">
+      <c r="E12" s="76" t="s">
         <v>522</v>
       </c>
-      <c r="F12" s="40"/>
-      <c r="G12" s="41" t="s">
+      <c r="F12" s="41"/>
+      <c r="G12" s="42" t="s">
         <v>523</v>
       </c>
       <c r="H12" s="28"/>
@@ -3254,25 +3257,25 @@
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="74">
+      <c r="A13" s="75">
         <v>6.0</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="120" t="s">
+      <c r="C13" s="121" t="s">
         <v>86</v>
       </c>
-      <c r="D13" s="75" t="s">
+      <c r="D13" s="76" t="s">
         <v>395</v>
       </c>
-      <c r="E13" s="75" t="s">
+      <c r="E13" s="76" t="s">
         <v>524</v>
       </c>
-      <c r="F13" s="119">
+      <c r="F13" s="120">
         <v>25.0</v>
       </c>
-      <c r="G13" s="120" t="s">
+      <c r="G13" s="121" t="s">
         <v>525</v>
       </c>
       <c r="H13" s="28"/>
@@ -3290,25 +3293,25 @@
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="74">
+      <c r="A14" s="75">
         <v>7.0</v>
       </c>
-      <c r="B14" s="75" t="s">
+      <c r="B14" s="76" t="s">
         <v>102</v>
       </c>
-      <c r="C14" s="120" t="s">
+      <c r="C14" s="121" t="s">
         <v>94</v>
       </c>
-      <c r="D14" s="75" t="s">
+      <c r="D14" s="76" t="s">
         <v>395</v>
       </c>
-      <c r="E14" s="75" t="s">
+      <c r="E14" s="76" t="s">
         <v>526</v>
       </c>
-      <c r="F14" s="119">
+      <c r="F14" s="120">
         <v>30.0</v>
       </c>
-      <c r="G14" s="120" t="s">
+      <c r="G14" s="121" t="s">
         <v>525</v>
       </c>
       <c r="H14" s="28"/>
@@ -3326,7 +3329,7 @@
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="74">
+      <c r="A15" s="75">
         <v>8.0</v>
       </c>
       <c r="B15" s="3" t="s">
@@ -3335,16 +3338,16 @@
       <c r="C15" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D15" s="75" t="s">
+      <c r="D15" s="76" t="s">
         <v>527</v>
       </c>
-      <c r="E15" s="75" t="s">
+      <c r="E15" s="76" t="s">
         <v>524</v>
       </c>
-      <c r="F15" s="119">
+      <c r="F15" s="120">
         <v>22.0</v>
       </c>
-      <c r="G15" s="120" t="s">
+      <c r="G15" s="121" t="s">
         <v>525</v>
       </c>
       <c r="H15" s="28"/>
@@ -3362,23 +3365,23 @@
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="74">
+      <c r="A16" s="75">
         <v>9.0</v>
       </c>
-      <c r="B16" s="75" t="s">
+      <c r="B16" s="76" t="s">
         <v>102</v>
       </c>
-      <c r="C16" s="41" t="s">
+      <c r="C16" s="42" t="s">
         <v>94</v>
       </c>
-      <c r="D16" s="75" t="s">
+      <c r="D16" s="76" t="s">
         <v>362</v>
       </c>
-      <c r="E16" s="75" t="s">
+      <c r="E16" s="76" t="s">
         <v>528</v>
       </c>
-      <c r="F16" s="40"/>
-      <c r="G16" s="41" t="s">
+      <c r="F16" s="41"/>
+      <c r="G16" s="42" t="s">
         <v>529</v>
       </c>
       <c r="H16" s="28"/>
@@ -3396,25 +3399,25 @@
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="76">
+      <c r="A17" s="77">
         <v>10.0</v>
       </c>
-      <c r="B17" s="75" t="s">
+      <c r="B17" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="C17" s="120" t="s">
+      <c r="C17" s="121" t="s">
         <v>86</v>
       </c>
-      <c r="D17" s="75" t="s">
+      <c r="D17" s="76" t="s">
         <v>530</v>
       </c>
-      <c r="E17" s="75" t="s">
+      <c r="E17" s="76" t="s">
         <v>531</v>
       </c>
-      <c r="F17" s="119">
+      <c r="F17" s="120">
         <v>27.0</v>
       </c>
-      <c r="G17" s="120" t="s">
+      <c r="G17" s="121" t="s">
         <v>517</v>
       </c>
       <c r="H17" s="31"/>
@@ -3432,25 +3435,25 @@
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="74">
+      <c r="A18" s="75">
         <v>11.0</v>
       </c>
-      <c r="B18" s="75" t="s">
+      <c r="B18" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="C18" s="120" t="s">
+      <c r="C18" s="121" t="s">
         <v>94</v>
       </c>
-      <c r="D18" s="75" t="s">
+      <c r="D18" s="76" t="s">
         <v>532</v>
       </c>
-      <c r="E18" s="75" t="s">
+      <c r="E18" s="76" t="s">
         <v>533</v>
       </c>
-      <c r="F18" s="119">
+      <c r="F18" s="120">
         <v>23.0</v>
       </c>
-      <c r="G18" s="120" t="s">
+      <c r="G18" s="121" t="s">
         <v>525</v>
       </c>
       <c r="H18" s="28"/>
@@ -3468,25 +3471,25 @@
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="76">
+      <c r="A19" s="77">
         <v>12.0</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C19" s="120" t="s">
+      <c r="C19" s="121" t="s">
         <v>76</v>
       </c>
-      <c r="D19" s="75" t="s">
+      <c r="D19" s="76" t="s">
         <v>179</v>
       </c>
-      <c r="E19" s="75" t="s">
+      <c r="E19" s="76" t="s">
         <v>534</v>
       </c>
-      <c r="F19" s="119">
+      <c r="F19" s="120">
         <v>30.0</v>
       </c>
-      <c r="G19" s="120" t="s">
+      <c r="G19" s="121" t="s">
         <v>517</v>
       </c>
       <c r="H19" s="31"/>
@@ -3504,23 +3507,23 @@
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="76">
+      <c r="A20" s="77">
         <v>13.0</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C20" s="120" t="s">
+      <c r="C20" s="121" t="s">
         <v>86</v>
       </c>
-      <c r="D20" s="75" t="s">
+      <c r="D20" s="76" t="s">
         <v>535</v>
       </c>
-      <c r="E20" s="75" t="s">
+      <c r="E20" s="76" t="s">
         <v>536</v>
       </c>
       <c r="F20" s="3"/>
-      <c r="G20" s="120" t="s">
+      <c r="G20" s="121" t="s">
         <v>525</v>
       </c>
       <c r="H20" s="31"/>
@@ -3538,25 +3541,25 @@
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="76">
+      <c r="A21" s="77">
         <v>14.0</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C21" s="120" t="s">
+      <c r="C21" s="121" t="s">
         <v>94</v>
       </c>
-      <c r="D21" s="75" t="s">
+      <c r="D21" s="76" t="s">
         <v>537</v>
       </c>
-      <c r="E21" s="75" t="s">
+      <c r="E21" s="76" t="s">
         <v>538</v>
       </c>
-      <c r="F21" s="119">
+      <c r="F21" s="120">
         <v>18.0</v>
       </c>
-      <c r="G21" s="120" t="s">
+      <c r="G21" s="121" t="s">
         <v>523</v>
       </c>
       <c r="H21" s="31"/>
@@ -3574,25 +3577,25 @@
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="74">
+      <c r="A22" s="75">
         <v>15.0</v>
       </c>
-      <c r="B22" s="121" t="s">
+      <c r="B22" s="122" t="s">
         <v>102</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D22" s="75" t="s">
+      <c r="D22" s="76" t="s">
         <v>362</v>
       </c>
-      <c r="E22" s="75" t="s">
+      <c r="E22" s="76" t="s">
         <v>539</v>
       </c>
-      <c r="F22" s="119">
+      <c r="F22" s="120">
         <v>23.0</v>
       </c>
-      <c r="G22" s="120" t="s">
+      <c r="G22" s="121" t="s">
         <v>525</v>
       </c>
       <c r="H22" s="28"/>
@@ -3610,25 +3613,25 @@
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="76">
+      <c r="A23" s="77">
         <v>16.0</v>
       </c>
-      <c r="B23" s="121" t="s">
+      <c r="B23" s="122" t="s">
         <v>102</v>
       </c>
-      <c r="C23" s="120" t="s">
+      <c r="C23" s="121" t="s">
         <v>86</v>
       </c>
-      <c r="D23" s="75" t="s">
+      <c r="D23" s="76" t="s">
         <v>540</v>
       </c>
-      <c r="E23" s="75" t="s">
+      <c r="E23" s="76" t="s">
         <v>516</v>
       </c>
-      <c r="F23" s="119">
+      <c r="F23" s="120">
         <v>22.0</v>
       </c>
-      <c r="G23" s="120" t="s">
+      <c r="G23" s="121" t="s">
         <v>525</v>
       </c>
       <c r="H23" s="31"/>
@@ -3646,25 +3649,25 @@
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="122">
+      <c r="A24" s="123">
         <v>17.0</v>
       </c>
-      <c r="B24" s="123" t="s">
+      <c r="B24" s="124" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="124" t="s">
+      <c r="C24" s="125" t="s">
         <v>94</v>
       </c>
-      <c r="D24" s="83" t="s">
+      <c r="D24" s="84" t="s">
         <v>541</v>
       </c>
-      <c r="E24" s="83" t="s">
+      <c r="E24" s="84" t="s">
         <v>185</v>
       </c>
-      <c r="F24" s="119">
+      <c r="F24" s="120">
         <v>30.0</v>
       </c>
-      <c r="G24" s="120" t="s">
+      <c r="G24" s="121" t="s">
         <v>517</v>
       </c>
       <c r="H24" s="28"/>
@@ -3682,25 +3685,25 @@
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="74">
+      <c r="A25" s="75">
         <v>18.0</v>
       </c>
-      <c r="B25" s="75" t="s">
+      <c r="B25" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="C25" s="120" t="s">
+      <c r="C25" s="121" t="s">
         <v>94</v>
       </c>
-      <c r="D25" s="75" t="s">
+      <c r="D25" s="76" t="s">
         <v>357</v>
       </c>
-      <c r="E25" s="75" t="s">
+      <c r="E25" s="76" t="s">
         <v>542</v>
       </c>
-      <c r="F25" s="119">
+      <c r="F25" s="120">
         <v>19.0</v>
       </c>
-      <c r="G25" s="120" t="s">
+      <c r="G25" s="121" t="s">
         <v>525</v>
       </c>
       <c r="H25" s="28"/>
@@ -3718,23 +3721,23 @@
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="76">
+      <c r="A26" s="77">
         <v>19.0</v>
       </c>
-      <c r="B26" s="75" t="s">
+      <c r="B26" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="C26" s="120" t="s">
+      <c r="C26" s="121" t="s">
         <v>94</v>
       </c>
-      <c r="D26" s="75" t="s">
+      <c r="D26" s="76" t="s">
         <v>543</v>
       </c>
-      <c r="E26" s="75" t="s">
+      <c r="E26" s="76" t="s">
         <v>544</v>
       </c>
-      <c r="F26" s="40"/>
-      <c r="G26" s="41" t="s">
+      <c r="F26" s="41"/>
+      <c r="G26" s="42" t="s">
         <v>523</v>
       </c>
       <c r="H26" s="31"/>
@@ -3752,23 +3755,23 @@
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="125">
+      <c r="A27" s="126">
         <v>20.0</v>
       </c>
-      <c r="B27" s="75" t="s">
+      <c r="B27" s="76" t="s">
         <v>102</v>
       </c>
-      <c r="C27" s="41" t="s">
+      <c r="C27" s="42" t="s">
         <v>94</v>
       </c>
-      <c r="D27" s="75" t="s">
+      <c r="D27" s="76" t="s">
         <v>545</v>
       </c>
-      <c r="E27" s="75" t="s">
+      <c r="E27" s="76" t="s">
         <v>533</v>
       </c>
       <c r="F27" s="3"/>
-      <c r="G27" s="120" t="s">
+      <c r="G27" s="121" t="s">
         <v>523</v>
       </c>
       <c r="H27" s="31"/>
@@ -3786,61 +3789,61 @@
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="122">
+      <c r="A28" s="123">
         <v>21.0</v>
       </c>
-      <c r="B28" s="123" t="s">
+      <c r="B28" s="124" t="s">
         <v>67</v>
       </c>
-      <c r="C28" s="124" t="s">
+      <c r="C28" s="125" t="s">
         <v>94</v>
       </c>
-      <c r="D28" s="83" t="s">
+      <c r="D28" s="84" t="s">
         <v>546</v>
       </c>
-      <c r="E28" s="83" t="s">
+      <c r="E28" s="84" t="s">
         <v>547</v>
       </c>
-      <c r="F28" s="102">
+      <c r="F28" s="103">
         <v>23.0</v>
       </c>
-      <c r="G28" s="103" t="s">
+      <c r="G28" s="104" t="s">
         <v>523</v>
       </c>
-      <c r="H28" s="66"/>
-      <c r="I28" s="67"/>
-      <c r="J28" s="67"/>
-      <c r="K28" s="67"/>
-      <c r="L28" s="67"/>
-      <c r="M28" s="67"/>
-      <c r="N28" s="67"/>
-      <c r="O28" s="67"/>
-      <c r="P28" s="67"/>
-      <c r="Q28" s="66">
+      <c r="H28" s="67"/>
+      <c r="I28" s="68"/>
+      <c r="J28" s="68"/>
+      <c r="K28" s="68"/>
+      <c r="L28" s="68"/>
+      <c r="M28" s="68"/>
+      <c r="N28" s="68"/>
+      <c r="O28" s="68"/>
+      <c r="P28" s="68"/>
+      <c r="Q28" s="67">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
-      <c r="A29" s="76">
+      <c r="A29" s="77">
         <v>22.0</v>
       </c>
-      <c r="B29" s="75" t="s">
+      <c r="B29" s="76" t="s">
         <v>102</v>
       </c>
-      <c r="C29" s="41" t="s">
+      <c r="C29" s="42" t="s">
         <v>76</v>
       </c>
-      <c r="D29" s="75" t="s">
+      <c r="D29" s="76" t="s">
         <v>548</v>
       </c>
-      <c r="E29" s="75" t="s">
+      <c r="E29" s="76" t="s">
         <v>549</v>
       </c>
-      <c r="F29" s="40">
+      <c r="F29" s="41">
         <v>22.0</v>
       </c>
-      <c r="G29" s="41" t="s">
+      <c r="G29" s="42" t="s">
         <v>523</v>
       </c>
       <c r="H29" s="31"/>
@@ -3858,25 +3861,25 @@
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="76">
+      <c r="A30" s="77">
         <v>23.0</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C30" s="120" t="s">
+      <c r="C30" s="121" t="s">
         <v>86</v>
       </c>
-      <c r="D30" s="75" t="s">
+      <c r="D30" s="76" t="s">
         <v>550</v>
       </c>
-      <c r="E30" s="75" t="s">
+      <c r="E30" s="76" t="s">
         <v>551</v>
       </c>
-      <c r="F30" s="119">
+      <c r="F30" s="120">
         <v>21.0</v>
       </c>
-      <c r="G30" s="120" t="s">
+      <c r="G30" s="121" t="s">
         <v>552</v>
       </c>
       <c r="H30" s="31"/>
@@ -3894,25 +3897,25 @@
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="76">
+      <c r="A31" s="77">
         <v>24.0</v>
       </c>
-      <c r="B31" s="75" t="s">
+      <c r="B31" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="C31" s="41" t="s">
+      <c r="C31" s="42" t="s">
         <v>76</v>
       </c>
-      <c r="D31" s="126" t="s">
+      <c r="D31" s="127" t="s">
         <v>553</v>
       </c>
-      <c r="E31" s="75" t="s">
+      <c r="E31" s="76" t="s">
         <v>516</v>
       </c>
-      <c r="F31" s="40">
+      <c r="F31" s="41">
         <v>30.0</v>
       </c>
-      <c r="G31" s="41" t="s">
+      <c r="G31" s="42" t="s">
         <v>512</v>
       </c>
       <c r="H31" s="31"/>
@@ -3930,61 +3933,61 @@
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="76">
+      <c r="A32" s="77">
         <v>25.0</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C32" s="120" t="s">
+      <c r="C32" s="121" t="s">
         <v>76</v>
       </c>
-      <c r="D32" s="75" t="s">
+      <c r="D32" s="76" t="s">
         <v>554</v>
       </c>
-      <c r="E32" s="75" t="s">
+      <c r="E32" s="76" t="s">
         <v>555</v>
       </c>
-      <c r="F32" s="127">
+      <c r="F32" s="128">
         <v>23.0</v>
       </c>
-      <c r="G32" s="128" t="s">
+      <c r="G32" s="129" t="s">
         <v>556</v>
       </c>
-      <c r="H32" s="66"/>
-      <c r="I32" s="67"/>
-      <c r="J32" s="67"/>
-      <c r="K32" s="67"/>
-      <c r="L32" s="67"/>
-      <c r="M32" s="67"/>
-      <c r="N32" s="67"/>
-      <c r="O32" s="67"/>
-      <c r="P32" s="67"/>
-      <c r="Q32" s="66">
+      <c r="H32" s="67"/>
+      <c r="I32" s="68"/>
+      <c r="J32" s="68"/>
+      <c r="K32" s="68"/>
+      <c r="L32" s="68"/>
+      <c r="M32" s="68"/>
+      <c r="N32" s="68"/>
+      <c r="O32" s="68"/>
+      <c r="P32" s="68"/>
+      <c r="Q32" s="67">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="125">
+      <c r="A33" s="126">
         <v>26.0</v>
       </c>
-      <c r="B33" s="75" t="s">
+      <c r="B33" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="C33" s="120" t="s">
+      <c r="C33" s="121" t="s">
         <v>86</v>
       </c>
-      <c r="D33" s="75" t="s">
+      <c r="D33" s="76" t="s">
         <v>557</v>
       </c>
-      <c r="E33" s="75" t="s">
+      <c r="E33" s="76" t="s">
         <v>185</v>
       </c>
-      <c r="F33" s="119">
+      <c r="F33" s="120">
         <v>22.0</v>
       </c>
-      <c r="G33" s="120" t="s">
+      <c r="G33" s="121" t="s">
         <v>523</v>
       </c>
       <c r="H33" s="31"/>
@@ -4984,10 +4987,10 @@
       <c r="C28" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="D28" s="34" t="s">
+      <c r="D28" s="38" t="s">
         <v>124</v>
       </c>
-      <c r="E28" s="34" t="s">
+      <c r="E28" s="38" t="s">
         <v>125</v>
       </c>
       <c r="F28" s="26"/>
@@ -5334,10 +5337,10 @@
       <c r="H6" s="13"/>
     </row>
     <row r="7" ht="21.0" customHeight="1">
-      <c r="A7" s="38" t="s">
+      <c r="A7" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="38" t="s">
+      <c r="B7" s="39" t="s">
         <v>141</v>
       </c>
       <c r="C7" s="20" t="s">
@@ -5396,14 +5399,14 @@
       <c r="C8" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="39" t="s">
+      <c r="D8" s="40" t="s">
         <v>142</v>
       </c>
       <c r="E8" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="F8" s="40"/>
-      <c r="G8" s="41"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="42"/>
       <c r="H8" s="28"/>
       <c r="I8" s="29"/>
       <c r="J8" s="29"/>
@@ -5434,8 +5437,8 @@
       <c r="E9" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="F9" s="40"/>
-      <c r="G9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="42"/>
       <c r="H9" s="31"/>
       <c r="I9" s="32"/>
       <c r="J9" s="32"/>
@@ -5466,8 +5469,8 @@
       <c r="E10" s="23" t="s">
         <v>147</v>
       </c>
-      <c r="F10" s="40"/>
-      <c r="G10" s="41"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="42"/>
       <c r="H10" s="28"/>
       <c r="I10" s="29"/>
       <c r="J10" s="29"/>
@@ -5498,8 +5501,8 @@
       <c r="E11" s="23" t="s">
         <v>149</v>
       </c>
-      <c r="F11" s="40"/>
-      <c r="G11" s="41"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="42"/>
       <c r="H11" s="31"/>
       <c r="I11" s="32"/>
       <c r="J11" s="32"/>
@@ -5530,8 +5533,8 @@
       <c r="E12" s="23" t="s">
         <v>151</v>
       </c>
-      <c r="F12" s="40"/>
-      <c r="G12" s="41"/>
+      <c r="F12" s="41"/>
+      <c r="G12" s="42"/>
       <c r="H12" s="28"/>
       <c r="I12" s="29"/>
       <c r="J12" s="29"/>
@@ -5562,8 +5565,8 @@
       <c r="E13" s="23" t="s">
         <v>153</v>
       </c>
-      <c r="F13" s="40"/>
-      <c r="G13" s="41"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="42"/>
       <c r="H13" s="31"/>
       <c r="I13" s="32"/>
       <c r="J13" s="32"/>
@@ -5594,8 +5597,8 @@
       <c r="E14" s="23" t="s">
         <v>155</v>
       </c>
-      <c r="F14" s="40"/>
-      <c r="G14" s="41"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="42"/>
       <c r="H14" s="28"/>
       <c r="I14" s="29"/>
       <c r="J14" s="29"/>
@@ -5626,8 +5629,8 @@
       <c r="E15" s="23" t="s">
         <v>157</v>
       </c>
-      <c r="F15" s="40"/>
-      <c r="G15" s="41"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="42"/>
       <c r="H15" s="31"/>
       <c r="I15" s="32"/>
       <c r="J15" s="32"/>
@@ -5643,7 +5646,7 @@
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="42">
+      <c r="A16" s="43">
         <v>9.0</v>
       </c>
       <c r="B16" s="23" t="s">
@@ -5652,14 +5655,14 @@
       <c r="C16" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="D16" s="43" t="s">
+      <c r="D16" s="44" t="s">
         <v>158</v>
       </c>
-      <c r="E16" s="43" t="s">
+      <c r="E16" s="44" t="s">
         <v>159</v>
       </c>
-      <c r="F16" s="40"/>
-      <c r="G16" s="41"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="42"/>
       <c r="H16" s="31"/>
       <c r="I16" s="32"/>
       <c r="J16" s="32"/>
@@ -5690,8 +5693,8 @@
       <c r="E17" s="23" t="s">
         <v>161</v>
       </c>
-      <c r="F17" s="40"/>
-      <c r="G17" s="41"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="42"/>
       <c r="H17" s="31"/>
       <c r="I17" s="32"/>
       <c r="J17" s="32"/>
@@ -5722,8 +5725,8 @@
       <c r="E18" s="23" t="s">
         <v>162</v>
       </c>
-      <c r="F18" s="40"/>
-      <c r="G18" s="41"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="42"/>
       <c r="H18" s="28"/>
       <c r="I18" s="29"/>
       <c r="J18" s="29"/>
@@ -5754,8 +5757,8 @@
       <c r="E19" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="F19" s="40"/>
-      <c r="G19" s="41"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="42"/>
       <c r="H19" s="31"/>
       <c r="I19" s="32"/>
       <c r="J19" s="32"/>
@@ -5783,11 +5786,11 @@
       <c r="D20" s="23" t="s">
         <v>165</v>
       </c>
-      <c r="E20" s="44" t="s">
+      <c r="E20" s="45" t="s">
         <v>153</v>
       </c>
-      <c r="F20" s="40"/>
-      <c r="G20" s="41"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="42"/>
       <c r="H20" s="28"/>
       <c r="I20" s="29"/>
       <c r="J20" s="29"/>
@@ -5818,8 +5821,8 @@
       <c r="E21" s="23" t="s">
         <v>157</v>
       </c>
-      <c r="F21" s="40"/>
-      <c r="G21" s="41"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="42"/>
       <c r="H21" s="31"/>
       <c r="I21" s="32"/>
       <c r="J21" s="32"/>
@@ -5844,14 +5847,14 @@
       <c r="C22" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="D22" s="45" t="s">
+      <c r="D22" s="46" t="s">
         <v>166</v>
       </c>
-      <c r="E22" s="45" t="s">
+      <c r="E22" s="46" t="s">
         <v>167</v>
       </c>
-      <c r="F22" s="40"/>
-      <c r="G22" s="41"/>
+      <c r="F22" s="41"/>
+      <c r="G22" s="42"/>
       <c r="H22" s="28"/>
       <c r="I22" s="29"/>
       <c r="J22" s="29"/>
@@ -5873,17 +5876,17 @@
       <c r="B23" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="C23" s="46" t="s">
+      <c r="C23" s="47" t="s">
         <v>86</v>
       </c>
-      <c r="D23" s="47" t="s">
+      <c r="D23" s="48" t="s">
         <v>168</v>
       </c>
-      <c r="E23" s="47" t="s">
+      <c r="E23" s="48" t="s">
         <v>167</v>
       </c>
-      <c r="F23" s="40"/>
-      <c r="G23" s="41"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="42"/>
       <c r="H23" s="31"/>
       <c r="I23" s="32"/>
       <c r="J23" s="32"/>
@@ -5914,8 +5917,8 @@
       <c r="E24" s="23" t="s">
         <v>170</v>
       </c>
-      <c r="F24" s="40"/>
-      <c r="G24" s="41"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="42"/>
       <c r="H24" s="28"/>
       <c r="I24" s="29"/>
       <c r="J24" s="29"/>
@@ -5946,8 +5949,8 @@
       <c r="E25" s="23" t="s">
         <v>172</v>
       </c>
-      <c r="F25" s="40"/>
-      <c r="G25" s="41"/>
+      <c r="F25" s="41"/>
+      <c r="G25" s="42"/>
       <c r="H25" s="31"/>
       <c r="I25" s="32"/>
       <c r="J25" s="32"/>
@@ -5978,8 +5981,8 @@
       <c r="E26" s="23" t="s">
         <v>174</v>
       </c>
-      <c r="F26" s="40"/>
-      <c r="G26" s="41"/>
+      <c r="F26" s="41"/>
+      <c r="G26" s="42"/>
       <c r="H26" s="28"/>
       <c r="I26" s="29"/>
       <c r="J26" s="29"/>
@@ -5995,7 +5998,7 @@
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="48">
+      <c r="A27" s="49">
         <v>20.0</v>
       </c>
       <c r="B27" s="23" t="s">
@@ -6010,8 +6013,8 @@
       <c r="E27" s="23" t="s">
         <v>176</v>
       </c>
-      <c r="F27" s="40"/>
-      <c r="G27" s="41"/>
+      <c r="F27" s="41"/>
+      <c r="G27" s="42"/>
       <c r="H27" s="28"/>
       <c r="I27" s="29"/>
       <c r="J27" s="29"/>
@@ -6042,8 +6045,8 @@
       <c r="E28" s="23" t="s">
         <v>155</v>
       </c>
-      <c r="F28" s="40"/>
-      <c r="G28" s="41"/>
+      <c r="F28" s="41"/>
+      <c r="G28" s="42"/>
       <c r="H28" s="28"/>
       <c r="I28" s="29"/>
       <c r="J28" s="29"/>
@@ -6074,8 +6077,8 @@
       <c r="E29" s="23" t="s">
         <v>178</v>
       </c>
-      <c r="F29" s="40"/>
-      <c r="G29" s="41"/>
+      <c r="F29" s="41"/>
+      <c r="G29" s="42"/>
       <c r="H29" s="31"/>
       <c r="I29" s="32"/>
       <c r="J29" s="32"/>
@@ -6106,8 +6109,8 @@
       <c r="E30" s="23" t="s">
         <v>153</v>
       </c>
-      <c r="F30" s="40"/>
-      <c r="G30" s="41"/>
+      <c r="F30" s="41"/>
+      <c r="G30" s="42"/>
       <c r="H30" s="28"/>
       <c r="I30" s="29"/>
       <c r="J30" s="29"/>
@@ -6132,14 +6135,14 @@
       <c r="C31" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="D31" s="43" t="s">
+      <c r="D31" s="44" t="s">
         <v>180</v>
       </c>
-      <c r="E31" s="43" t="s">
+      <c r="E31" s="44" t="s">
         <v>181</v>
       </c>
-      <c r="F31" s="40"/>
-      <c r="G31" s="41"/>
+      <c r="F31" s="41"/>
+      <c r="G31" s="42"/>
       <c r="H31" s="31"/>
       <c r="I31" s="32"/>
       <c r="J31" s="32"/>
@@ -6170,8 +6173,8 @@
       <c r="E32" s="23" t="s">
         <v>183</v>
       </c>
-      <c r="F32" s="40"/>
-      <c r="G32" s="41"/>
+      <c r="F32" s="41"/>
+      <c r="G32" s="42"/>
       <c r="H32" s="28"/>
       <c r="I32" s="29"/>
       <c r="J32" s="29"/>
@@ -6193,17 +6196,17 @@
       <c r="B33" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="C33" s="46" t="s">
+      <c r="C33" s="47" t="s">
         <v>86</v>
       </c>
-      <c r="D33" s="47" t="s">
+      <c r="D33" s="48" t="s">
         <v>184</v>
       </c>
-      <c r="E33" s="47" t="s">
+      <c r="E33" s="48" t="s">
         <v>185</v>
       </c>
-      <c r="F33" s="40"/>
-      <c r="G33" s="41"/>
+      <c r="F33" s="41"/>
+      <c r="G33" s="42"/>
       <c r="H33" s="31"/>
       <c r="I33" s="32"/>
       <c r="J33" s="32"/>
@@ -6366,13 +6369,13 @@
       <c r="H6" s="13"/>
     </row>
     <row r="7" ht="21.0" customHeight="1">
-      <c r="A7" s="38" t="s">
+      <c r="A7" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="38" t="s">
+      <c r="B7" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="C7" s="49" t="s">
+      <c r="C7" s="50" t="s">
         <v>52</v>
       </c>
       <c r="D7" s="20" t="s">
@@ -6419,23 +6422,23 @@
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="50">
+      <c r="A8" s="51">
         <v>1.0</v>
       </c>
-      <c r="B8" s="51" t="s">
+      <c r="B8" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="C8" s="52" t="s">
+      <c r="C8" s="53" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="53" t="s">
+      <c r="D8" s="54" t="s">
         <v>191</v>
       </c>
-      <c r="E8" s="53" t="s">
+      <c r="E8" s="54" t="s">
         <v>192</v>
       </c>
-      <c r="F8" s="54"/>
-      <c r="G8" s="55" t="s">
+      <c r="F8" s="55"/>
+      <c r="G8" s="56" t="s">
         <v>193</v>
       </c>
       <c r="H8" s="28"/>
@@ -6453,23 +6456,23 @@
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="56">
+      <c r="A9" s="57">
         <v>2.0</v>
       </c>
-      <c r="B9" s="51" t="s">
+      <c r="B9" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="52" t="s">
+      <c r="C9" s="53" t="s">
         <v>76</v>
       </c>
-      <c r="D9" s="57" t="s">
+      <c r="D9" s="58" t="s">
         <v>194</v>
       </c>
-      <c r="E9" s="57" t="s">
+      <c r="E9" s="58" t="s">
         <v>195</v>
       </c>
-      <c r="F9" s="58"/>
-      <c r="G9" s="58" t="s">
+      <c r="F9" s="59"/>
+      <c r="G9" s="59" t="s">
         <v>186</v>
       </c>
       <c r="H9" s="28"/>
@@ -6487,23 +6490,23 @@
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="56">
+      <c r="A10" s="57">
         <v>3.0</v>
       </c>
-      <c r="B10" s="51" t="s">
+      <c r="B10" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="C10" s="52" t="s">
+      <c r="C10" s="53" t="s">
         <v>76</v>
       </c>
-      <c r="D10" s="57" t="s">
+      <c r="D10" s="58" t="s">
         <v>196</v>
       </c>
-      <c r="E10" s="57" t="s">
+      <c r="E10" s="58" t="s">
         <v>197</v>
       </c>
-      <c r="F10" s="54"/>
-      <c r="G10" s="55" t="s">
+      <c r="F10" s="55"/>
+      <c r="G10" s="56" t="s">
         <v>186</v>
       </c>
       <c r="H10" s="28"/>
@@ -6521,23 +6524,23 @@
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="50">
+      <c r="A11" s="51">
         <v>4.0</v>
       </c>
-      <c r="B11" s="51" t="s">
+      <c r="B11" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="C11" s="52" t="s">
+      <c r="C11" s="53" t="s">
         <v>76</v>
       </c>
-      <c r="D11" s="53" t="s">
+      <c r="D11" s="54" t="s">
         <v>198</v>
       </c>
-      <c r="E11" s="53" t="s">
+      <c r="E11" s="54" t="s">
         <v>199</v>
       </c>
-      <c r="F11" s="59"/>
-      <c r="G11" s="58" t="s">
+      <c r="F11" s="60"/>
+      <c r="G11" s="59" t="s">
         <v>186</v>
       </c>
       <c r="H11" s="31"/>
@@ -6555,23 +6558,23 @@
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="50">
+      <c r="A12" s="51">
         <v>5.0</v>
       </c>
-      <c r="B12" s="51" t="s">
+      <c r="B12" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="52" t="s">
+      <c r="C12" s="53" t="s">
         <v>86</v>
       </c>
-      <c r="D12" s="53" t="s">
+      <c r="D12" s="54" t="s">
         <v>200</v>
       </c>
-      <c r="E12" s="53" t="s">
+      <c r="E12" s="54" t="s">
         <v>201</v>
       </c>
-      <c r="F12" s="54"/>
-      <c r="G12" s="55" t="s">
+      <c r="F12" s="55"/>
+      <c r="G12" s="56" t="s">
         <v>186</v>
       </c>
       <c r="H12" s="28"/>
@@ -6589,23 +6592,23 @@
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="50">
+      <c r="A13" s="51">
         <v>6.0</v>
       </c>
-      <c r="B13" s="51" t="s">
+      <c r="B13" s="52" t="s">
         <v>102</v>
       </c>
-      <c r="C13" s="52" t="s">
+      <c r="C13" s="53" t="s">
         <v>86</v>
       </c>
-      <c r="D13" s="53" t="s">
+      <c r="D13" s="54" t="s">
         <v>202</v>
       </c>
-      <c r="E13" s="53" t="s">
+      <c r="E13" s="54" t="s">
         <v>203</v>
       </c>
-      <c r="F13" s="59"/>
-      <c r="G13" s="58" t="s">
+      <c r="F13" s="60"/>
+      <c r="G13" s="59" t="s">
         <v>120</v>
       </c>
       <c r="H13" s="31"/>
@@ -6623,23 +6626,23 @@
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="56">
+      <c r="A14" s="57">
         <v>7.0</v>
       </c>
-      <c r="B14" s="51" t="s">
+      <c r="B14" s="52" t="s">
         <v>102</v>
       </c>
-      <c r="C14" s="52" t="s">
+      <c r="C14" s="53" t="s">
         <v>94</v>
       </c>
-      <c r="D14" s="57" t="s">
+      <c r="D14" s="58" t="s">
         <v>204</v>
       </c>
-      <c r="E14" s="57" t="s">
+      <c r="E14" s="58" t="s">
         <v>205</v>
       </c>
-      <c r="F14" s="59"/>
-      <c r="G14" s="58" t="s">
+      <c r="F14" s="60"/>
+      <c r="G14" s="59" t="s">
         <v>186</v>
       </c>
       <c r="H14" s="31"/>
@@ -6657,23 +6660,23 @@
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="50">
+      <c r="A15" s="51">
         <v>8.0</v>
       </c>
-      <c r="B15" s="51" t="s">
+      <c r="B15" s="52" t="s">
         <v>102</v>
       </c>
-      <c r="C15" s="52" t="s">
+      <c r="C15" s="53" t="s">
         <v>86</v>
       </c>
-      <c r="D15" s="53" t="s">
+      <c r="D15" s="54" t="s">
         <v>206</v>
       </c>
-      <c r="E15" s="53" t="s">
+      <c r="E15" s="54" t="s">
         <v>207</v>
       </c>
-      <c r="F15" s="59"/>
-      <c r="G15" s="58" t="s">
+      <c r="F15" s="60"/>
+      <c r="G15" s="59" t="s">
         <v>186</v>
       </c>
       <c r="H15" s="31"/>
@@ -6691,23 +6694,23 @@
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="50">
+      <c r="A16" s="51">
         <v>9.0</v>
       </c>
-      <c r="B16" s="51" t="s">
+      <c r="B16" s="52" t="s">
         <v>102</v>
       </c>
-      <c r="C16" s="52" t="s">
+      <c r="C16" s="53" t="s">
         <v>76</v>
       </c>
-      <c r="D16" s="53" t="s">
+      <c r="D16" s="54" t="s">
         <v>208</v>
       </c>
-      <c r="E16" s="53" t="s">
+      <c r="E16" s="54" t="s">
         <v>209</v>
       </c>
-      <c r="F16" s="60"/>
-      <c r="G16" s="61" t="s">
+      <c r="F16" s="61"/>
+      <c r="G16" s="62" t="s">
         <v>186</v>
       </c>
       <c r="H16" s="31"/>
@@ -6725,23 +6728,23 @@
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="50">
+      <c r="A17" s="51">
         <v>10.0</v>
       </c>
-      <c r="B17" s="51" t="s">
+      <c r="B17" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="C17" s="52" t="s">
+      <c r="C17" s="53" t="s">
         <v>94</v>
       </c>
-      <c r="D17" s="53" t="s">
+      <c r="D17" s="54" t="s">
         <v>210</v>
       </c>
-      <c r="E17" s="53" t="s">
+      <c r="E17" s="54" t="s">
         <v>211</v>
       </c>
-      <c r="F17" s="54"/>
-      <c r="G17" s="55" t="s">
+      <c r="F17" s="55"/>
+      <c r="G17" s="56" t="s">
         <v>186</v>
       </c>
       <c r="H17" s="28"/>
@@ -6759,23 +6762,23 @@
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="62">
+      <c r="A18" s="63">
         <v>11.0</v>
       </c>
-      <c r="B18" s="51" t="s">
+      <c r="B18" s="52" t="s">
         <v>102</v>
       </c>
-      <c r="C18" s="52" t="s">
+      <c r="C18" s="53" t="s">
         <v>86</v>
       </c>
-      <c r="D18" s="57" t="s">
+      <c r="D18" s="58" t="s">
         <v>212</v>
       </c>
-      <c r="E18" s="57" t="s">
+      <c r="E18" s="58" t="s">
         <v>213</v>
       </c>
-      <c r="F18" s="54"/>
-      <c r="G18" s="55" t="s">
+      <c r="F18" s="55"/>
+      <c r="G18" s="56" t="s">
         <v>186</v>
       </c>
       <c r="H18" s="28"/>
@@ -6793,23 +6796,23 @@
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="50">
+      <c r="A19" s="51">
         <v>12.0</v>
       </c>
-      <c r="B19" s="51" t="s">
+      <c r="B19" s="52" t="s">
         <v>102</v>
       </c>
-      <c r="C19" s="52" t="s">
+      <c r="C19" s="53" t="s">
         <v>76</v>
       </c>
-      <c r="D19" s="53" t="s">
+      <c r="D19" s="54" t="s">
         <v>214</v>
       </c>
-      <c r="E19" s="53" t="s">
+      <c r="E19" s="54" t="s">
         <v>215</v>
       </c>
-      <c r="F19" s="54"/>
-      <c r="G19" s="55" t="s">
+      <c r="F19" s="55"/>
+      <c r="G19" s="56" t="s">
         <v>186</v>
       </c>
       <c r="H19" s="28"/>
@@ -6827,23 +6830,23 @@
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="63">
+      <c r="A20" s="64">
         <v>13.0</v>
       </c>
-      <c r="B20" s="51" t="s">
+      <c r="B20" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="C20" s="52" t="s">
+      <c r="C20" s="53" t="s">
         <v>86</v>
       </c>
-      <c r="D20" s="53" t="s">
+      <c r="D20" s="54" t="s">
         <v>216</v>
       </c>
-      <c r="E20" s="53" t="s">
+      <c r="E20" s="54" t="s">
         <v>217</v>
       </c>
-      <c r="F20" s="54"/>
-      <c r="G20" s="55" t="s">
+      <c r="F20" s="55"/>
+      <c r="G20" s="56" t="s">
         <v>186</v>
       </c>
       <c r="H20" s="28"/>
@@ -6861,57 +6864,57 @@
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="62">
+      <c r="A21" s="63">
         <v>14.0</v>
       </c>
-      <c r="B21" s="51" t="s">
+      <c r="B21" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="C21" s="52" t="s">
+      <c r="C21" s="53" t="s">
         <v>86</v>
       </c>
-      <c r="D21" s="57" t="s">
+      <c r="D21" s="58" t="s">
         <v>218</v>
       </c>
-      <c r="E21" s="57" t="s">
+      <c r="E21" s="58" t="s">
         <v>219</v>
       </c>
-      <c r="F21" s="64"/>
-      <c r="G21" s="65" t="s">
+      <c r="F21" s="65"/>
+      <c r="G21" s="66" t="s">
         <v>186</v>
       </c>
-      <c r="H21" s="66"/>
-      <c r="I21" s="67"/>
-      <c r="J21" s="67"/>
-      <c r="K21" s="67"/>
-      <c r="L21" s="67"/>
-      <c r="M21" s="67"/>
-      <c r="N21" s="67"/>
-      <c r="O21" s="67"/>
-      <c r="P21" s="67"/>
-      <c r="Q21" s="66">
+      <c r="H21" s="67"/>
+      <c r="I21" s="68"/>
+      <c r="J21" s="68"/>
+      <c r="K21" s="68"/>
+      <c r="L21" s="68"/>
+      <c r="M21" s="68"/>
+      <c r="N21" s="68"/>
+      <c r="O21" s="68"/>
+      <c r="P21" s="68"/>
+      <c r="Q21" s="67">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="56">
+      <c r="A22" s="57">
         <v>15.0</v>
       </c>
-      <c r="B22" s="51" t="s">
+      <c r="B22" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="C22" s="52" t="s">
+      <c r="C22" s="53" t="s">
         <v>94</v>
       </c>
-      <c r="D22" s="57" t="s">
+      <c r="D22" s="58" t="s">
         <v>220</v>
       </c>
-      <c r="E22" s="57" t="s">
+      <c r="E22" s="58" t="s">
         <v>221</v>
       </c>
-      <c r="F22" s="59"/>
-      <c r="G22" s="58" t="s">
+      <c r="F22" s="60"/>
+      <c r="G22" s="59" t="s">
         <v>186</v>
       </c>
       <c r="H22" s="31"/>
@@ -6929,23 +6932,23 @@
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="50">
+      <c r="A23" s="51">
         <v>16.0</v>
       </c>
-      <c r="B23" s="51" t="s">
+      <c r="B23" s="52" t="s">
         <v>102</v>
       </c>
-      <c r="C23" s="52" t="s">
+      <c r="C23" s="53" t="s">
         <v>86</v>
       </c>
-      <c r="D23" s="53" t="s">
+      <c r="D23" s="54" t="s">
         <v>222</v>
       </c>
-      <c r="E23" s="53" t="s">
+      <c r="E23" s="54" t="s">
         <v>223</v>
       </c>
-      <c r="F23" s="59"/>
-      <c r="G23" s="58" t="s">
+      <c r="F23" s="60"/>
+      <c r="G23" s="59" t="s">
         <v>186</v>
       </c>
       <c r="H23" s="31"/>
@@ -6963,23 +6966,23 @@
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="62">
+      <c r="A24" s="63">
         <v>17.0</v>
       </c>
-      <c r="B24" s="51" t="s">
+      <c r="B24" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="52" t="s">
+      <c r="C24" s="53" t="s">
         <v>94</v>
       </c>
-      <c r="D24" s="68" t="s">
+      <c r="D24" s="69" t="s">
         <v>224</v>
       </c>
-      <c r="E24" s="68" t="s">
+      <c r="E24" s="69" t="s">
         <v>225</v>
       </c>
-      <c r="F24" s="54"/>
-      <c r="G24" s="55" t="s">
+      <c r="F24" s="55"/>
+      <c r="G24" s="56" t="s">
         <v>186</v>
       </c>
       <c r="H24" s="31"/>
@@ -6997,23 +7000,23 @@
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="63">
+      <c r="A25" s="64">
         <v>18.0</v>
       </c>
-      <c r="B25" s="51" t="s">
+      <c r="B25" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="C25" s="52" t="s">
+      <c r="C25" s="53" t="s">
         <v>86</v>
       </c>
-      <c r="D25" s="53" t="s">
+      <c r="D25" s="54" t="s">
         <v>226</v>
       </c>
-      <c r="E25" s="53" t="s">
+      <c r="E25" s="54" t="s">
         <v>227</v>
       </c>
-      <c r="F25" s="59"/>
-      <c r="G25" s="58" t="s">
+      <c r="F25" s="60"/>
+      <c r="G25" s="59" t="s">
         <v>186</v>
       </c>
       <c r="H25" s="28"/>
@@ -7031,23 +7034,23 @@
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="63">
+      <c r="A26" s="64">
         <v>19.0</v>
       </c>
-      <c r="B26" s="51" t="s">
+      <c r="B26" s="52" t="s">
         <v>102</v>
       </c>
-      <c r="C26" s="69" t="s">
+      <c r="C26" s="70" t="s">
         <v>94</v>
       </c>
-      <c r="D26" s="68" t="s">
+      <c r="D26" s="69" t="s">
         <v>228</v>
       </c>
-      <c r="E26" s="68" t="s">
+      <c r="E26" s="69" t="s">
         <v>229</v>
       </c>
-      <c r="F26" s="55"/>
-      <c r="G26" s="55" t="s">
+      <c r="F26" s="56"/>
+      <c r="G26" s="56" t="s">
         <v>230</v>
       </c>
       <c r="H26" s="31"/>
@@ -7065,23 +7068,23 @@
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="50">
+      <c r="A27" s="51">
         <v>20.0</v>
       </c>
-      <c r="B27" s="51" t="s">
+      <c r="B27" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="C27" s="52" t="s">
+      <c r="C27" s="53" t="s">
         <v>86</v>
       </c>
-      <c r="D27" s="53" t="s">
+      <c r="D27" s="54" t="s">
         <v>231</v>
       </c>
-      <c r="E27" s="53" t="s">
+      <c r="E27" s="54" t="s">
         <v>232</v>
       </c>
-      <c r="F27" s="54"/>
-      <c r="G27" s="55" t="s">
+      <c r="F27" s="55"/>
+      <c r="G27" s="56" t="s">
         <v>186</v>
       </c>
       <c r="H27" s="28"/>
@@ -7099,23 +7102,23 @@
       </c>
     </row>
     <row r="28" ht="17.25" customHeight="1">
-      <c r="A28" s="56">
+      <c r="A28" s="57">
         <v>21.0</v>
       </c>
-      <c r="B28" s="51" t="s">
+      <c r="B28" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="C28" s="52" t="s">
+      <c r="C28" s="53" t="s">
         <v>76</v>
       </c>
-      <c r="D28" s="57" t="s">
+      <c r="D28" s="58" t="s">
         <v>233</v>
       </c>
-      <c r="E28" s="57" t="s">
+      <c r="E28" s="58" t="s">
         <v>234</v>
       </c>
-      <c r="F28" s="70"/>
-      <c r="G28" s="61"/>
+      <c r="F28" s="71"/>
+      <c r="G28" s="62"/>
       <c r="H28" s="31"/>
       <c r="I28" s="32"/>
       <c r="J28" s="32"/>
@@ -7128,23 +7131,23 @@
       <c r="Q28" s="31"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="63">
+      <c r="A29" s="64">
         <v>22.0</v>
       </c>
-      <c r="B29" s="51" t="s">
+      <c r="B29" s="52" t="s">
         <v>102</v>
       </c>
-      <c r="C29" s="52" t="s">
+      <c r="C29" s="53" t="s">
         <v>86</v>
       </c>
-      <c r="D29" s="53" t="s">
+      <c r="D29" s="54" t="s">
         <v>235</v>
       </c>
-      <c r="E29" s="53" t="s">
+      <c r="E29" s="54" t="s">
         <v>236</v>
       </c>
-      <c r="F29" s="70"/>
-      <c r="G29" s="61" t="s">
+      <c r="F29" s="71"/>
+      <c r="G29" s="62" t="s">
         <v>237</v>
       </c>
       <c r="H29" s="28"/>
@@ -7162,23 +7165,23 @@
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="62">
+      <c r="A30" s="63">
         <v>23.0</v>
       </c>
-      <c r="B30" s="51" t="s">
+      <c r="B30" s="52" t="s">
         <v>102</v>
       </c>
-      <c r="C30" s="52" t="s">
+      <c r="C30" s="53" t="s">
         <v>76</v>
       </c>
-      <c r="D30" s="57" t="s">
+      <c r="D30" s="58" t="s">
         <v>238</v>
       </c>
-      <c r="E30" s="57" t="s">
+      <c r="E30" s="58" t="s">
         <v>239</v>
       </c>
-      <c r="F30" s="70"/>
-      <c r="G30" s="61"/>
+      <c r="F30" s="71"/>
+      <c r="G30" s="62"/>
       <c r="H30" s="31"/>
       <c r="I30" s="32"/>
       <c r="J30" s="32"/>
@@ -7194,23 +7197,23 @@
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="63">
+      <c r="A31" s="64">
         <v>24.0</v>
       </c>
-      <c r="B31" s="51" t="s">
+      <c r="B31" s="52" t="s">
         <v>102</v>
       </c>
-      <c r="C31" s="52" t="s">
+      <c r="C31" s="53" t="s">
         <v>94</v>
       </c>
-      <c r="D31" s="53" t="s">
+      <c r="D31" s="54" t="s">
         <v>240</v>
       </c>
-      <c r="E31" s="53" t="s">
+      <c r="E31" s="54" t="s">
         <v>241</v>
       </c>
-      <c r="F31" s="70"/>
-      <c r="G31" s="61"/>
+      <c r="F31" s="71"/>
+      <c r="G31" s="62"/>
       <c r="H31" s="28"/>
       <c r="I31" s="29"/>
       <c r="J31" s="29"/>
@@ -7226,23 +7229,23 @@
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="63">
+      <c r="A32" s="64">
         <v>25.0</v>
       </c>
-      <c r="B32" s="51" t="s">
+      <c r="B32" s="52" t="s">
         <v>102</v>
       </c>
-      <c r="C32" s="52" t="s">
+      <c r="C32" s="53" t="s">
         <v>76</v>
       </c>
-      <c r="D32" s="53" t="s">
+      <c r="D32" s="54" t="s">
         <v>242</v>
       </c>
-      <c r="E32" s="53" t="s">
+      <c r="E32" s="54" t="s">
         <v>243</v>
       </c>
-      <c r="F32" s="70"/>
-      <c r="G32" s="61"/>
+      <c r="F32" s="71"/>
+      <c r="G32" s="62"/>
       <c r="H32" s="31"/>
       <c r="I32" s="32"/>
       <c r="J32" s="32"/>
@@ -7258,23 +7261,23 @@
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="50">
+      <c r="A33" s="51">
         <v>26.0</v>
       </c>
-      <c r="B33" s="51" t="s">
+      <c r="B33" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="C33" s="52" t="s">
+      <c r="C33" s="53" t="s">
         <v>94</v>
       </c>
-      <c r="D33" s="71" t="s">
+      <c r="D33" s="72" t="s">
         <v>244</v>
       </c>
-      <c r="E33" s="53" t="s">
+      <c r="E33" s="54" t="s">
         <v>245</v>
       </c>
-      <c r="F33" s="59"/>
-      <c r="G33" s="58" t="s">
+      <c r="F33" s="60"/>
+      <c r="G33" s="59" t="s">
         <v>186</v>
       </c>
       <c r="H33" s="31"/>
@@ -7292,13 +7295,13 @@
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="63"/>
-      <c r="B34" s="51"/>
-      <c r="C34" s="52"/>
-      <c r="D34" s="53"/>
-      <c r="E34" s="53"/>
-      <c r="F34" s="72"/>
-      <c r="G34" s="73"/>
+      <c r="A34" s="64"/>
+      <c r="B34" s="52"/>
+      <c r="C34" s="53"/>
+      <c r="D34" s="54"/>
+      <c r="E34" s="54"/>
+      <c r="F34" s="73"/>
+      <c r="G34" s="74"/>
       <c r="H34" s="31"/>
       <c r="I34" s="32"/>
       <c r="J34" s="32"/>
@@ -7448,10 +7451,10 @@
       <c r="H6" s="13"/>
     </row>
     <row r="7" ht="21.0" customHeight="1">
-      <c r="A7" s="38" t="s">
+      <c r="A7" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="38" t="s">
+      <c r="B7" s="39" t="s">
         <v>51</v>
       </c>
       <c r="C7" s="20" t="s">
@@ -7501,23 +7504,23 @@
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="74">
+      <c r="A8" s="75">
         <v>1.0</v>
       </c>
-      <c r="B8" s="75" t="s">
+      <c r="B8" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="C8" s="41" t="s">
+      <c r="C8" s="42" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="75" t="s">
+      <c r="D8" s="76" t="s">
         <v>246</v>
       </c>
-      <c r="E8" s="75" t="s">
+      <c r="E8" s="76" t="s">
         <v>247</v>
       </c>
-      <c r="F8" s="40"/>
-      <c r="G8" s="41"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="42"/>
       <c r="H8" s="28"/>
       <c r="I8" s="29"/>
       <c r="J8" s="29"/>
@@ -7533,21 +7536,21 @@
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="76">
+      <c r="A9" s="77">
         <v>2.0</v>
       </c>
-      <c r="B9" s="75" t="s">
+      <c r="B9" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="C9" s="41"/>
-      <c r="D9" s="75" t="s">
+      <c r="C9" s="42"/>
+      <c r="D9" s="76" t="s">
         <v>248</v>
       </c>
-      <c r="E9" s="75" t="s">
+      <c r="E9" s="76" t="s">
         <v>249</v>
       </c>
-      <c r="F9" s="40"/>
-      <c r="G9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="42"/>
       <c r="H9" s="31"/>
       <c r="I9" s="32"/>
       <c r="J9" s="32"/>
@@ -7563,21 +7566,21 @@
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="74">
+      <c r="A10" s="75">
         <v>3.0</v>
       </c>
-      <c r="B10" s="75" t="s">
+      <c r="B10" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="C10" s="41"/>
-      <c r="D10" s="75" t="s">
+      <c r="C10" s="42"/>
+      <c r="D10" s="76" t="s">
         <v>250</v>
       </c>
-      <c r="E10" s="75" t="s">
+      <c r="E10" s="76" t="s">
         <v>251</v>
       </c>
-      <c r="F10" s="40"/>
-      <c r="G10" s="41"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="42"/>
       <c r="H10" s="28"/>
       <c r="I10" s="29"/>
       <c r="J10" s="29"/>
@@ -7593,21 +7596,21 @@
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="76">
+      <c r="A11" s="77">
         <v>4.0</v>
       </c>
-      <c r="B11" s="75" t="s">
+      <c r="B11" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="C11" s="41"/>
-      <c r="D11" s="75" t="s">
+      <c r="C11" s="42"/>
+      <c r="D11" s="76" t="s">
         <v>252</v>
       </c>
-      <c r="E11" s="75" t="s">
+      <c r="E11" s="76" t="s">
         <v>253</v>
       </c>
-      <c r="F11" s="40"/>
-      <c r="G11" s="41"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="42"/>
       <c r="H11" s="31"/>
       <c r="I11" s="32"/>
       <c r="J11" s="32"/>
@@ -7623,21 +7626,21 @@
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="74">
+      <c r="A12" s="75">
         <v>5.0</v>
       </c>
-      <c r="B12" s="75" t="s">
+      <c r="B12" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="C12" s="41"/>
-      <c r="D12" s="75" t="s">
+      <c r="C12" s="42"/>
+      <c r="D12" s="76" t="s">
         <v>254</v>
       </c>
-      <c r="E12" s="75" t="s">
+      <c r="E12" s="76" t="s">
         <v>255</v>
       </c>
-      <c r="F12" s="40"/>
-      <c r="G12" s="41"/>
+      <c r="F12" s="41"/>
+      <c r="G12" s="42"/>
       <c r="H12" s="28"/>
       <c r="I12" s="29"/>
       <c r="J12" s="29"/>
@@ -7653,21 +7656,21 @@
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="76">
+      <c r="A13" s="77">
         <v>6.0</v>
       </c>
-      <c r="B13" s="75" t="s">
+      <c r="B13" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="41"/>
-      <c r="D13" s="75" t="s">
+      <c r="C13" s="42"/>
+      <c r="D13" s="76" t="s">
         <v>256</v>
       </c>
-      <c r="E13" s="75" t="s">
+      <c r="E13" s="76" t="s">
         <v>257</v>
       </c>
-      <c r="F13" s="40"/>
-      <c r="G13" s="41"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="42"/>
       <c r="H13" s="31"/>
       <c r="I13" s="32"/>
       <c r="J13" s="32"/>
@@ -7683,21 +7686,21 @@
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="74">
+      <c r="A14" s="75">
         <v>7.0</v>
       </c>
-      <c r="B14" s="75" t="s">
+      <c r="B14" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="41"/>
-      <c r="D14" s="75" t="s">
+      <c r="C14" s="42"/>
+      <c r="D14" s="76" t="s">
         <v>258</v>
       </c>
-      <c r="E14" s="75" t="s">
+      <c r="E14" s="76" t="s">
         <v>259</v>
       </c>
-      <c r="F14" s="40"/>
-      <c r="G14" s="41"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="42"/>
       <c r="H14" s="28"/>
       <c r="I14" s="29"/>
       <c r="J14" s="29"/>
@@ -7713,21 +7716,21 @@
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="76">
+      <c r="A15" s="77">
         <v>8.0</v>
       </c>
-      <c r="B15" s="75" t="s">
+      <c r="B15" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="C15" s="41"/>
-      <c r="D15" s="75" t="s">
+      <c r="C15" s="42"/>
+      <c r="D15" s="76" t="s">
         <v>260</v>
       </c>
-      <c r="E15" s="75" t="s">
+      <c r="E15" s="76" t="s">
         <v>261</v>
       </c>
-      <c r="F15" s="40"/>
-      <c r="G15" s="41"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="42"/>
       <c r="H15" s="31"/>
       <c r="I15" s="32"/>
       <c r="J15" s="32"/>
@@ -7743,21 +7746,21 @@
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="74">
+      <c r="A16" s="75">
         <v>9.0</v>
       </c>
-      <c r="B16" s="75" t="s">
+      <c r="B16" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="C16" s="41"/>
-      <c r="D16" s="75" t="s">
+      <c r="C16" s="42"/>
+      <c r="D16" s="76" t="s">
         <v>262</v>
       </c>
-      <c r="E16" s="75" t="s">
+      <c r="E16" s="76" t="s">
         <v>255</v>
       </c>
-      <c r="F16" s="40"/>
-      <c r="G16" s="41"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="42"/>
       <c r="H16" s="28"/>
       <c r="I16" s="29"/>
       <c r="J16" s="29"/>
@@ -7773,21 +7776,21 @@
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="76">
+      <c r="A17" s="77">
         <v>10.0</v>
       </c>
-      <c r="B17" s="75" t="s">
+      <c r="B17" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="41"/>
-      <c r="D17" s="75" t="s">
+      <c r="C17" s="42"/>
+      <c r="D17" s="76" t="s">
         <v>263</v>
       </c>
-      <c r="E17" s="75" t="s">
+      <c r="E17" s="76" t="s">
         <v>264</v>
       </c>
-      <c r="F17" s="40"/>
-      <c r="G17" s="41"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="42"/>
       <c r="H17" s="31"/>
       <c r="I17" s="32"/>
       <c r="J17" s="32"/>
@@ -7803,21 +7806,21 @@
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="74">
+      <c r="A18" s="75">
         <v>11.0</v>
       </c>
-      <c r="B18" s="75" t="s">
+      <c r="B18" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="C18" s="41"/>
-      <c r="D18" s="75" t="s">
+      <c r="C18" s="42"/>
+      <c r="D18" s="76" t="s">
         <v>265</v>
       </c>
-      <c r="E18" s="75" t="s">
+      <c r="E18" s="76" t="s">
         <v>257</v>
       </c>
-      <c r="F18" s="40"/>
-      <c r="G18" s="41"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="42"/>
       <c r="H18" s="28"/>
       <c r="I18" s="29"/>
       <c r="J18" s="29"/>
@@ -7833,21 +7836,21 @@
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="76">
+      <c r="A19" s="77">
         <v>12.0</v>
       </c>
-      <c r="B19" s="75" t="s">
+      <c r="B19" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="C19" s="41"/>
-      <c r="D19" s="75" t="s">
+      <c r="C19" s="42"/>
+      <c r="D19" s="76" t="s">
         <v>266</v>
       </c>
-      <c r="E19" s="75" t="s">
+      <c r="E19" s="76" t="s">
         <v>267</v>
       </c>
-      <c r="F19" s="40"/>
-      <c r="G19" s="41"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="42"/>
       <c r="H19" s="31"/>
       <c r="I19" s="32"/>
       <c r="J19" s="32"/>
@@ -7863,21 +7866,21 @@
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="74">
+      <c r="A20" s="75">
         <v>13.0</v>
       </c>
-      <c r="B20" s="75" t="s">
+      <c r="B20" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="41"/>
-      <c r="D20" s="75" t="s">
+      <c r="C20" s="42"/>
+      <c r="D20" s="76" t="s">
         <v>268</v>
       </c>
-      <c r="E20" s="77" t="s">
+      <c r="E20" s="78" t="s">
         <v>269</v>
       </c>
-      <c r="F20" s="40"/>
-      <c r="G20" s="41"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="42"/>
       <c r="H20" s="28"/>
       <c r="I20" s="29"/>
       <c r="J20" s="29"/>
@@ -7893,21 +7896,21 @@
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="76">
+      <c r="A21" s="77">
         <v>14.0</v>
       </c>
-      <c r="B21" s="75" t="s">
+      <c r="B21" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="C21" s="41"/>
-      <c r="D21" s="75" t="s">
+      <c r="C21" s="42"/>
+      <c r="D21" s="76" t="s">
         <v>270</v>
       </c>
-      <c r="E21" s="75" t="s">
+      <c r="E21" s="76" t="s">
         <v>271</v>
       </c>
-      <c r="F21" s="40"/>
-      <c r="G21" s="41"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="42"/>
       <c r="H21" s="31"/>
       <c r="I21" s="32"/>
       <c r="J21" s="32"/>
@@ -7923,21 +7926,21 @@
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="74">
+      <c r="A22" s="75">
         <v>15.0</v>
       </c>
-      <c r="B22" s="75" t="s">
+      <c r="B22" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="C22" s="41"/>
-      <c r="D22" s="75" t="s">
+      <c r="C22" s="42"/>
+      <c r="D22" s="76" t="s">
         <v>272</v>
       </c>
-      <c r="E22" s="75" t="s">
+      <c r="E22" s="76" t="s">
         <v>273</v>
       </c>
-      <c r="F22" s="40"/>
-      <c r="G22" s="41"/>
+      <c r="F22" s="41"/>
+      <c r="G22" s="42"/>
       <c r="H22" s="28"/>
       <c r="I22" s="29"/>
       <c r="J22" s="29"/>
@@ -7953,21 +7956,21 @@
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="76">
+      <c r="A23" s="77">
         <v>16.0</v>
       </c>
-      <c r="B23" s="75" t="s">
+      <c r="B23" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="C23" s="41"/>
-      <c r="D23" s="78" t="s">
+      <c r="C23" s="42"/>
+      <c r="D23" s="79" t="s">
         <v>274</v>
       </c>
-      <c r="E23" s="78" t="s">
+      <c r="E23" s="79" t="s">
         <v>275</v>
       </c>
-      <c r="F23" s="40"/>
-      <c r="G23" s="41"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="42"/>
       <c r="H23" s="31"/>
       <c r="I23" s="32"/>
       <c r="J23" s="32"/>
@@ -7983,21 +7986,21 @@
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="74">
+      <c r="A24" s="75">
         <v>17.0</v>
       </c>
-      <c r="B24" s="75" t="s">
+      <c r="B24" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="C24" s="41"/>
-      <c r="D24" s="78" t="s">
+      <c r="C24" s="42"/>
+      <c r="D24" s="79" t="s">
         <v>276</v>
       </c>
-      <c r="E24" s="78" t="s">
+      <c r="E24" s="79" t="s">
         <v>277</v>
       </c>
-      <c r="F24" s="40"/>
-      <c r="G24" s="41"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="42"/>
       <c r="H24" s="28"/>
       <c r="I24" s="29"/>
       <c r="J24" s="29"/>
@@ -8013,21 +8016,21 @@
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="76">
+      <c r="A25" s="77">
         <v>18.0</v>
       </c>
-      <c r="B25" s="75" t="s">
+      <c r="B25" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="C25" s="41"/>
-      <c r="D25" s="75" t="s">
+      <c r="C25" s="42"/>
+      <c r="D25" s="76" t="s">
         <v>278</v>
       </c>
-      <c r="E25" s="75" t="s">
+      <c r="E25" s="76" t="s">
         <v>279</v>
       </c>
-      <c r="F25" s="40"/>
-      <c r="G25" s="41"/>
+      <c r="F25" s="41"/>
+      <c r="G25" s="42"/>
       <c r="H25" s="31"/>
       <c r="I25" s="32"/>
       <c r="J25" s="32"/>
@@ -8043,21 +8046,21 @@
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="74">
+      <c r="A26" s="75">
         <v>19.0</v>
       </c>
-      <c r="B26" s="75" t="s">
+      <c r="B26" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="C26" s="41"/>
-      <c r="D26" s="78" t="s">
+      <c r="C26" s="42"/>
+      <c r="D26" s="79" t="s">
         <v>280</v>
       </c>
-      <c r="E26" s="78" t="s">
+      <c r="E26" s="79" t="s">
         <v>281</v>
       </c>
-      <c r="F26" s="40"/>
-      <c r="G26" s="41"/>
+      <c r="F26" s="41"/>
+      <c r="G26" s="42"/>
       <c r="H26" s="28"/>
       <c r="I26" s="29"/>
       <c r="J26" s="29"/>
@@ -8073,21 +8076,21 @@
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="76">
+      <c r="A27" s="77">
         <v>20.0</v>
       </c>
-      <c r="B27" s="75" t="s">
+      <c r="B27" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="C27" s="41"/>
-      <c r="D27" s="75" t="s">
+      <c r="C27" s="42"/>
+      <c r="D27" s="76" t="s">
         <v>282</v>
       </c>
-      <c r="E27" s="75" t="s">
+      <c r="E27" s="76" t="s">
         <v>283</v>
       </c>
-      <c r="F27" s="40"/>
-      <c r="G27" s="41"/>
+      <c r="F27" s="41"/>
+      <c r="G27" s="42"/>
       <c r="H27" s="31"/>
       <c r="I27" s="32"/>
       <c r="J27" s="32"/>
@@ -8103,21 +8106,21 @@
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="74">
+      <c r="A28" s="75">
         <v>21.0</v>
       </c>
-      <c r="B28" s="75" t="s">
+      <c r="B28" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="C28" s="41"/>
-      <c r="D28" s="75" t="s">
+      <c r="C28" s="42"/>
+      <c r="D28" s="76" t="s">
         <v>284</v>
       </c>
-      <c r="E28" s="75" t="s">
+      <c r="E28" s="76" t="s">
         <v>285</v>
       </c>
-      <c r="F28" s="40"/>
-      <c r="G28" s="41"/>
+      <c r="F28" s="41"/>
+      <c r="G28" s="42"/>
       <c r="H28" s="28"/>
       <c r="I28" s="29"/>
       <c r="J28" s="29"/>
@@ -8133,21 +8136,21 @@
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
-      <c r="A29" s="76">
+      <c r="A29" s="77">
         <v>22.0</v>
       </c>
-      <c r="B29" s="75" t="s">
+      <c r="B29" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="C29" s="41"/>
-      <c r="D29" s="75" t="s">
+      <c r="C29" s="42"/>
+      <c r="D29" s="76" t="s">
         <v>286</v>
       </c>
-      <c r="E29" s="75" t="s">
+      <c r="E29" s="76" t="s">
         <v>287</v>
       </c>
-      <c r="F29" s="40"/>
-      <c r="G29" s="41"/>
+      <c r="F29" s="41"/>
+      <c r="G29" s="42"/>
       <c r="H29" s="31"/>
       <c r="I29" s="32"/>
       <c r="J29" s="32"/>
@@ -8163,21 +8166,21 @@
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="74">
+      <c r="A30" s="75">
         <v>23.0</v>
       </c>
-      <c r="B30" s="75" t="s">
+      <c r="B30" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="C30" s="41"/>
-      <c r="D30" s="75" t="s">
+      <c r="C30" s="42"/>
+      <c r="D30" s="76" t="s">
         <v>272</v>
       </c>
-      <c r="E30" s="75" t="s">
+      <c r="E30" s="76" t="s">
         <v>288</v>
       </c>
-      <c r="F30" s="40"/>
-      <c r="G30" s="41"/>
+      <c r="F30" s="41"/>
+      <c r="G30" s="42"/>
       <c r="H30" s="28"/>
       <c r="I30" s="29"/>
       <c r="J30" s="29"/>
@@ -8193,21 +8196,21 @@
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="76">
+      <c r="A31" s="77">
         <v>24.0</v>
       </c>
-      <c r="B31" s="75" t="s">
+      <c r="B31" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="C31" s="41"/>
-      <c r="D31" s="75" t="s">
+      <c r="C31" s="42"/>
+      <c r="D31" s="76" t="s">
         <v>289</v>
       </c>
-      <c r="E31" s="77" t="s">
+      <c r="E31" s="78" t="s">
         <v>290</v>
       </c>
-      <c r="F31" s="40"/>
-      <c r="G31" s="41"/>
+      <c r="F31" s="41"/>
+      <c r="G31" s="42"/>
       <c r="H31" s="31"/>
       <c r="I31" s="32"/>
       <c r="J31" s="32"/>
@@ -8223,21 +8226,21 @@
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="74">
+      <c r="A32" s="75">
         <v>25.0</v>
       </c>
-      <c r="B32" s="75" t="s">
+      <c r="B32" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="C32" s="41"/>
-      <c r="D32" s="75" t="s">
+      <c r="C32" s="42"/>
+      <c r="D32" s="76" t="s">
         <v>291</v>
       </c>
-      <c r="E32" s="75" t="s">
+      <c r="E32" s="76" t="s">
         <v>292</v>
       </c>
-      <c r="F32" s="40"/>
-      <c r="G32" s="41"/>
+      <c r="F32" s="41"/>
+      <c r="G32" s="42"/>
       <c r="H32" s="28"/>
       <c r="I32" s="29"/>
       <c r="J32" s="29"/>
@@ -8253,21 +8256,21 @@
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="76">
+      <c r="A33" s="77">
         <v>26.0</v>
       </c>
-      <c r="B33" s="75" t="s">
+      <c r="B33" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="C33" s="41"/>
-      <c r="D33" s="75" t="s">
+      <c r="C33" s="42"/>
+      <c r="D33" s="76" t="s">
         <v>262</v>
       </c>
-      <c r="E33" s="75" t="s">
+      <c r="E33" s="76" t="s">
         <v>293</v>
       </c>
-      <c r="F33" s="40"/>
-      <c r="G33" s="41"/>
+      <c r="F33" s="41"/>
+      <c r="G33" s="42"/>
       <c r="H33" s="31"/>
       <c r="I33" s="32"/>
       <c r="J33" s="32"/>
@@ -8384,7 +8387,7 @@
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
       <c r="D3" s="6"/>
-      <c r="E3" s="79" t="s">
+      <c r="E3" s="80" t="s">
         <v>296</v>
       </c>
       <c r="F3" s="5"/>
@@ -8430,10 +8433,10 @@
       <c r="H6" s="13"/>
     </row>
     <row r="7" ht="21.0" customHeight="1">
-      <c r="A7" s="38" t="s">
+      <c r="A7" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="38" t="s">
+      <c r="B7" s="39" t="s">
         <v>51</v>
       </c>
       <c r="C7" s="20" t="s">
@@ -8483,25 +8486,25 @@
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="74">
+      <c r="A8" s="75">
         <v>1.0</v>
       </c>
-      <c r="B8" s="75" t="s">
+      <c r="B8" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="C8" s="41" t="s">
+      <c r="C8" s="42" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="75" t="s">
+      <c r="D8" s="76" t="s">
         <v>299</v>
       </c>
-      <c r="E8" s="75" t="s">
+      <c r="E8" s="76" t="s">
         <v>300</v>
       </c>
-      <c r="F8" s="40">
+      <c r="F8" s="41">
         <v>37.0</v>
       </c>
-      <c r="G8" s="41" t="s">
+      <c r="G8" s="42" t="s">
         <v>294</v>
       </c>
       <c r="H8" s="28"/>
@@ -8519,25 +8522,25 @@
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="76">
+      <c r="A9" s="77">
         <v>2.0</v>
       </c>
-      <c r="B9" s="75" t="s">
+      <c r="B9" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="41" t="s">
+      <c r="C9" s="42" t="s">
         <v>86</v>
       </c>
-      <c r="D9" s="80" t="s">
+      <c r="D9" s="81" t="s">
         <v>301</v>
       </c>
-      <c r="E9" s="81" t="s">
+      <c r="E9" s="82" t="s">
         <v>302</v>
       </c>
-      <c r="F9" s="40">
+      <c r="F9" s="41">
         <v>32.0</v>
       </c>
-      <c r="G9" s="41" t="s">
+      <c r="G9" s="42" t="s">
         <v>294</v>
       </c>
       <c r="H9" s="31"/>
@@ -8555,25 +8558,25 @@
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="74">
+      <c r="A10" s="75">
         <v>3.0</v>
       </c>
-      <c r="B10" s="75" t="s">
+      <c r="B10" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="C10" s="41" t="s">
+      <c r="C10" s="42" t="s">
         <v>76</v>
       </c>
-      <c r="D10" s="75" t="s">
+      <c r="D10" s="76" t="s">
         <v>303</v>
       </c>
-      <c r="E10" s="75" t="s">
+      <c r="E10" s="76" t="s">
         <v>304</v>
       </c>
-      <c r="F10" s="40">
+      <c r="F10" s="41">
         <v>25.0</v>
       </c>
-      <c r="G10" s="41" t="s">
+      <c r="G10" s="42" t="s">
         <v>294</v>
       </c>
       <c r="H10" s="28"/>
@@ -8591,25 +8594,25 @@
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="74">
+      <c r="A11" s="75">
         <v>4.0</v>
       </c>
-      <c r="B11" s="75" t="s">
+      <c r="B11" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="C11" s="41" t="s">
+      <c r="C11" s="42" t="s">
         <v>76</v>
       </c>
-      <c r="D11" s="75" t="s">
+      <c r="D11" s="76" t="s">
         <v>305</v>
       </c>
-      <c r="E11" s="75" t="s">
+      <c r="E11" s="76" t="s">
         <v>306</v>
       </c>
-      <c r="F11" s="40">
+      <c r="F11" s="41">
         <v>29.0</v>
       </c>
-      <c r="G11" s="41" t="s">
+      <c r="G11" s="42" t="s">
         <v>294</v>
       </c>
       <c r="H11" s="28"/>
@@ -8627,25 +8630,25 @@
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="76">
+      <c r="A12" s="77">
         <v>5.0</v>
       </c>
-      <c r="B12" s="75" t="s">
+      <c r="B12" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="41" t="s">
+      <c r="C12" s="42" t="s">
         <v>76</v>
       </c>
-      <c r="D12" s="75" t="s">
+      <c r="D12" s="76" t="s">
         <v>307</v>
       </c>
-      <c r="E12" s="75" t="s">
+      <c r="E12" s="76" t="s">
         <v>308</v>
       </c>
-      <c r="F12" s="40">
+      <c r="F12" s="41">
         <v>27.0</v>
       </c>
-      <c r="G12" s="41" t="s">
+      <c r="G12" s="42" t="s">
         <v>309</v>
       </c>
       <c r="H12" s="31"/>
@@ -8663,23 +8666,23 @@
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="76">
+      <c r="A13" s="77">
         <v>6.0</v>
       </c>
-      <c r="B13" s="75" t="s">
+      <c r="B13" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="C13" s="41" t="s">
+      <c r="C13" s="42" t="s">
         <v>86</v>
       </c>
-      <c r="D13" s="82" t="s">
+      <c r="D13" s="83" t="s">
         <v>310</v>
       </c>
-      <c r="E13" s="75" t="s">
+      <c r="E13" s="76" t="s">
         <v>311</v>
       </c>
-      <c r="F13" s="40"/>
-      <c r="G13" s="41" t="s">
+      <c r="F13" s="41"/>
+      <c r="G13" s="42" t="s">
         <v>294</v>
       </c>
       <c r="H13" s="31"/>
@@ -8697,25 +8700,25 @@
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="74">
+      <c r="A14" s="75">
         <v>7.0</v>
       </c>
-      <c r="B14" s="75" t="s">
+      <c r="B14" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="41" t="s">
+      <c r="C14" s="42" t="s">
         <v>86</v>
       </c>
-      <c r="D14" s="83" t="s">
+      <c r="D14" s="84" t="s">
         <v>312</v>
       </c>
-      <c r="E14" s="83" t="s">
+      <c r="E14" s="84" t="s">
         <v>313</v>
       </c>
-      <c r="F14" s="40">
+      <c r="F14" s="41">
         <v>23.0</v>
       </c>
-      <c r="G14" s="41" t="s">
+      <c r="G14" s="42" t="s">
         <v>294</v>
       </c>
       <c r="H14" s="28"/>
@@ -8733,25 +8736,25 @@
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="76">
+      <c r="A15" s="77">
         <v>8.0</v>
       </c>
-      <c r="B15" s="75" t="s">
+      <c r="B15" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="C15" s="41" t="s">
+      <c r="C15" s="42" t="s">
         <v>86</v>
       </c>
-      <c r="D15" s="75" t="s">
+      <c r="D15" s="76" t="s">
         <v>314</v>
       </c>
-      <c r="E15" s="75" t="s">
+      <c r="E15" s="76" t="s">
         <v>315</v>
       </c>
-      <c r="F15" s="40">
+      <c r="F15" s="41">
         <v>28.0</v>
       </c>
-      <c r="G15" s="41" t="s">
+      <c r="G15" s="42" t="s">
         <v>294</v>
       </c>
       <c r="H15" s="31"/>
@@ -8769,25 +8772,25 @@
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="74">
+      <c r="A16" s="75">
         <v>9.0</v>
       </c>
-      <c r="B16" s="75" t="s">
+      <c r="B16" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="C16" s="41" t="s">
+      <c r="C16" s="42" t="s">
         <v>94</v>
       </c>
-      <c r="D16" s="75" t="s">
+      <c r="D16" s="76" t="s">
         <v>316</v>
       </c>
-      <c r="E16" s="75" t="s">
+      <c r="E16" s="76" t="s">
         <v>317</v>
       </c>
-      <c r="F16" s="40">
+      <c r="F16" s="41">
         <v>40.0</v>
       </c>
-      <c r="G16" s="41" t="s">
+      <c r="G16" s="42" t="s">
         <v>294</v>
       </c>
       <c r="H16" s="28"/>
@@ -8805,25 +8808,25 @@
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="74">
+      <c r="A17" s="75">
         <v>10.0</v>
       </c>
-      <c r="B17" s="75" t="s">
+      <c r="B17" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="C17" s="41" t="s">
+      <c r="C17" s="42" t="s">
         <v>94</v>
       </c>
-      <c r="D17" s="75" t="s">
+      <c r="D17" s="76" t="s">
         <v>318</v>
       </c>
-      <c r="E17" s="75" t="s">
+      <c r="E17" s="76" t="s">
         <v>319</v>
       </c>
-      <c r="F17" s="40">
+      <c r="F17" s="41">
         <v>37.0</v>
       </c>
-      <c r="G17" s="41" t="s">
+      <c r="G17" s="42" t="s">
         <v>294</v>
       </c>
       <c r="H17" s="28"/>
@@ -8841,25 +8844,25 @@
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="76">
+      <c r="A18" s="77">
         <v>11.0</v>
       </c>
-      <c r="B18" s="75" t="s">
+      <c r="B18" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="C18" s="41" t="s">
+      <c r="C18" s="42" t="s">
         <v>86</v>
       </c>
-      <c r="D18" s="75" t="s">
+      <c r="D18" s="76" t="s">
         <v>320</v>
       </c>
-      <c r="E18" s="75" t="s">
+      <c r="E18" s="76" t="s">
         <v>321</v>
       </c>
-      <c r="F18" s="40">
+      <c r="F18" s="41">
         <v>32.0</v>
       </c>
-      <c r="G18" s="41" t="s">
+      <c r="G18" s="42" t="s">
         <v>294</v>
       </c>
       <c r="H18" s="31"/>
@@ -8877,25 +8880,25 @@
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="76">
+      <c r="A19" s="77">
         <v>12.0</v>
       </c>
-      <c r="B19" s="75" t="s">
+      <c r="B19" s="76" t="s">
         <v>121</v>
       </c>
-      <c r="C19" s="41" t="s">
+      <c r="C19" s="42" t="s">
         <v>94</v>
       </c>
-      <c r="D19" s="82" t="s">
+      <c r="D19" s="83" t="s">
         <v>322</v>
       </c>
-      <c r="E19" s="75" t="s">
+      <c r="E19" s="76" t="s">
         <v>323</v>
       </c>
-      <c r="F19" s="40">
+      <c r="F19" s="41">
         <v>20.0</v>
       </c>
-      <c r="G19" s="41" t="s">
+      <c r="G19" s="42" t="s">
         <v>294</v>
       </c>
       <c r="H19" s="31"/>
@@ -8913,23 +8916,23 @@
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="74">
+      <c r="A20" s="75">
         <v>13.0</v>
       </c>
-      <c r="B20" s="75" t="s">
+      <c r="B20" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="C20" s="41" t="s">
+      <c r="C20" s="42" t="s">
         <v>76</v>
       </c>
-      <c r="D20" s="83" t="s">
+      <c r="D20" s="84" t="s">
         <v>324</v>
       </c>
-      <c r="E20" s="83" t="s">
+      <c r="E20" s="84" t="s">
         <v>325</v>
       </c>
-      <c r="F20" s="40"/>
-      <c r="G20" s="41" t="s">
+      <c r="F20" s="41"/>
+      <c r="G20" s="42" t="s">
         <v>294</v>
       </c>
       <c r="H20" s="28"/>
@@ -8947,25 +8950,25 @@
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="76">
+      <c r="A21" s="77">
         <v>14.0</v>
       </c>
-      <c r="B21" s="75" t="s">
+      <c r="B21" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="C21" s="41" t="s">
+      <c r="C21" s="42" t="s">
         <v>86</v>
       </c>
-      <c r="D21" s="75" t="s">
+      <c r="D21" s="76" t="s">
         <v>326</v>
       </c>
-      <c r="E21" s="75" t="s">
+      <c r="E21" s="76" t="s">
         <v>327</v>
       </c>
-      <c r="F21" s="40">
+      <c r="F21" s="41">
         <v>33.0</v>
       </c>
-      <c r="G21" s="41" t="s">
+      <c r="G21" s="42" t="s">
         <v>294</v>
       </c>
       <c r="H21" s="31"/>
@@ -8983,25 +8986,25 @@
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="74">
+      <c r="A22" s="75">
         <v>15.0</v>
       </c>
-      <c r="B22" s="75" t="s">
+      <c r="B22" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="C22" s="41" t="s">
+      <c r="C22" s="42" t="s">
         <v>76</v>
       </c>
-      <c r="D22" s="78" t="s">
+      <c r="D22" s="79" t="s">
         <v>328</v>
       </c>
-      <c r="E22" s="78" t="s">
+      <c r="E22" s="79" t="s">
         <v>329</v>
       </c>
-      <c r="F22" s="40">
+      <c r="F22" s="41">
         <v>33.0</v>
       </c>
-      <c r="G22" s="41" t="s">
+      <c r="G22" s="42" t="s">
         <v>294</v>
       </c>
       <c r="H22" s="28"/>
@@ -9019,25 +9022,25 @@
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="76">
+      <c r="A23" s="77">
         <v>16.0</v>
       </c>
-      <c r="B23" s="75" t="s">
+      <c r="B23" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="C23" s="41" t="s">
+      <c r="C23" s="42" t="s">
         <v>68</v>
       </c>
-      <c r="D23" s="78" t="s">
+      <c r="D23" s="79" t="s">
         <v>330</v>
       </c>
-      <c r="E23" s="78" t="s">
+      <c r="E23" s="79" t="s">
         <v>329</v>
       </c>
-      <c r="F23" s="40">
+      <c r="F23" s="41">
         <v>41.0</v>
       </c>
-      <c r="G23" s="41" t="s">
+      <c r="G23" s="42" t="s">
         <v>294</v>
       </c>
       <c r="H23" s="31"/>
@@ -9055,25 +9058,25 @@
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="74">
+      <c r="A24" s="75">
         <v>17.0</v>
       </c>
-      <c r="B24" s="75" t="s">
+      <c r="B24" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="41" t="s">
+      <c r="C24" s="42" t="s">
         <v>94</v>
       </c>
-      <c r="D24" s="82" t="s">
+      <c r="D24" s="83" t="s">
         <v>331</v>
       </c>
-      <c r="E24" s="75" t="s">
+      <c r="E24" s="76" t="s">
         <v>332</v>
       </c>
-      <c r="F24" s="40">
+      <c r="F24" s="41">
         <v>20.0</v>
       </c>
-      <c r="G24" s="41" t="s">
+      <c r="G24" s="42" t="s">
         <v>294</v>
       </c>
       <c r="H24" s="28"/>
@@ -9091,25 +9094,25 @@
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="76">
+      <c r="A25" s="77">
         <v>18.0</v>
       </c>
-      <c r="B25" s="75" t="s">
+      <c r="B25" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="C25" s="41" t="s">
+      <c r="C25" s="42" t="s">
         <v>94</v>
       </c>
-      <c r="D25" s="78" t="s">
+      <c r="D25" s="79" t="s">
         <v>333</v>
       </c>
-      <c r="E25" s="78" t="s">
+      <c r="E25" s="79" t="s">
         <v>13</v>
       </c>
-      <c r="F25" s="40">
+      <c r="F25" s="41">
         <v>34.0</v>
       </c>
-      <c r="G25" s="41" t="s">
+      <c r="G25" s="42" t="s">
         <v>294</v>
       </c>
       <c r="H25" s="31"/>
@@ -9127,23 +9130,23 @@
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="74">
+      <c r="A26" s="75">
         <v>19.0</v>
       </c>
-      <c r="B26" s="75" t="s">
+      <c r="B26" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="C26" s="41" t="s">
+      <c r="C26" s="42" t="s">
         <v>94</v>
       </c>
-      <c r="D26" s="82" t="s">
+      <c r="D26" s="83" t="s">
         <v>334</v>
       </c>
-      <c r="E26" s="75" t="s">
+      <c r="E26" s="76" t="s">
         <v>335</v>
       </c>
-      <c r="F26" s="40"/>
-      <c r="G26" s="41" t="s">
+      <c r="F26" s="41"/>
+      <c r="G26" s="42" t="s">
         <v>294</v>
       </c>
       <c r="H26" s="28"/>
@@ -9161,25 +9164,25 @@
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="76">
+      <c r="A27" s="77">
         <v>20.0</v>
       </c>
-      <c r="B27" s="75" t="s">
+      <c r="B27" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="C27" s="41" t="s">
+      <c r="C27" s="42" t="s">
         <v>86</v>
       </c>
-      <c r="D27" s="82" t="s">
+      <c r="D27" s="83" t="s">
         <v>336</v>
       </c>
-      <c r="E27" s="75" t="s">
+      <c r="E27" s="76" t="s">
         <v>87</v>
       </c>
-      <c r="F27" s="40">
+      <c r="F27" s="41">
         <v>27.0</v>
       </c>
-      <c r="G27" s="41" t="s">
+      <c r="G27" s="42" t="s">
         <v>294</v>
       </c>
       <c r="H27" s="31"/>
@@ -9197,25 +9200,25 @@
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="76">
+      <c r="A28" s="77">
         <v>21.0</v>
       </c>
-      <c r="B28" s="75" t="s">
+      <c r="B28" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="C28" s="41" t="s">
+      <c r="C28" s="42" t="s">
         <v>76</v>
       </c>
-      <c r="D28" s="75" t="s">
+      <c r="D28" s="76" t="s">
         <v>337</v>
       </c>
-      <c r="E28" s="75" t="s">
+      <c r="E28" s="76" t="s">
         <v>338</v>
       </c>
-      <c r="F28" s="40">
+      <c r="F28" s="41">
         <v>32.0</v>
       </c>
-      <c r="G28" s="41" t="s">
+      <c r="G28" s="42" t="s">
         <v>294</v>
       </c>
       <c r="H28" s="31"/>
@@ -9233,25 +9236,25 @@
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
-      <c r="A29" s="76">
+      <c r="A29" s="77">
         <v>22.0</v>
       </c>
-      <c r="B29" s="75" t="s">
+      <c r="B29" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="C29" s="41" t="s">
+      <c r="C29" s="42" t="s">
         <v>86</v>
       </c>
-      <c r="D29" s="78" t="s">
+      <c r="D29" s="79" t="s">
         <v>339</v>
       </c>
-      <c r="E29" s="78" t="s">
+      <c r="E29" s="79" t="s">
         <v>340</v>
       </c>
-      <c r="F29" s="40">
+      <c r="F29" s="41">
         <v>28.0</v>
       </c>
-      <c r="G29" s="41" t="s">
+      <c r="G29" s="42" t="s">
         <v>294</v>
       </c>
       <c r="H29" s="31"/>
@@ -9269,25 +9272,25 @@
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="74">
+      <c r="A30" s="75">
         <v>23.0</v>
       </c>
-      <c r="B30" s="75" t="s">
+      <c r="B30" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="C30" s="41" t="s">
+      <c r="C30" s="42" t="s">
         <v>86</v>
       </c>
-      <c r="D30" s="84" t="s">
+      <c r="D30" s="85" t="s">
         <v>341</v>
       </c>
-      <c r="E30" s="84" t="s">
+      <c r="E30" s="85" t="s">
         <v>342</v>
       </c>
-      <c r="F30" s="40">
+      <c r="F30" s="41">
         <v>41.0</v>
       </c>
-      <c r="G30" s="41" t="s">
+      <c r="G30" s="42" t="s">
         <v>294</v>
       </c>
       <c r="H30" s="28"/>
@@ -9305,21 +9308,21 @@
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="74">
+      <c r="A31" s="75">
         <v>24.0</v>
       </c>
-      <c r="B31" s="75" t="s">
+      <c r="B31" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="C31" s="41" t="s">
+      <c r="C31" s="42" t="s">
         <v>86</v>
       </c>
-      <c r="D31" s="82"/>
-      <c r="E31" s="75"/>
-      <c r="F31" s="40">
+      <c r="D31" s="83"/>
+      <c r="E31" s="76"/>
+      <c r="F31" s="41">
         <v>36.0</v>
       </c>
-      <c r="G31" s="41" t="s">
+      <c r="G31" s="42" t="s">
         <v>294</v>
       </c>
       <c r="H31" s="28"/>
@@ -9337,25 +9340,25 @@
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="74">
+      <c r="A32" s="75">
         <v>25.0</v>
       </c>
-      <c r="B32" s="75" t="s">
+      <c r="B32" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="C32" s="41" t="s">
+      <c r="C32" s="42" t="s">
         <v>94</v>
       </c>
-      <c r="D32" s="75" t="s">
+      <c r="D32" s="76" t="s">
         <v>343</v>
       </c>
-      <c r="E32" s="75" t="s">
+      <c r="E32" s="76" t="s">
         <v>344</v>
       </c>
-      <c r="F32" s="40">
+      <c r="F32" s="41">
         <v>19.0</v>
       </c>
-      <c r="G32" s="41"/>
+      <c r="G32" s="42"/>
       <c r="H32" s="28"/>
       <c r="I32" s="29"/>
       <c r="J32" s="29"/>
@@ -9371,25 +9374,25 @@
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="76">
+      <c r="A33" s="77">
         <v>26.0</v>
       </c>
-      <c r="B33" s="75" t="s">
+      <c r="B33" s="76" t="s">
         <v>121</v>
       </c>
-      <c r="C33" s="41" t="s">
+      <c r="C33" s="42" t="s">
         <v>76</v>
       </c>
-      <c r="D33" s="78" t="s">
+      <c r="D33" s="79" t="s">
         <v>345</v>
       </c>
-      <c r="E33" s="78" t="s">
+      <c r="E33" s="79" t="s">
         <v>346</v>
       </c>
-      <c r="F33" s="40">
+      <c r="F33" s="41">
         <v>19.0</v>
       </c>
-      <c r="G33" s="41"/>
+      <c r="G33" s="42"/>
       <c r="H33" s="31"/>
       <c r="I33" s="32"/>
       <c r="J33" s="32"/>
@@ -9469,12 +9472,12 @@
       <c r="C1" s="5"/>
       <c r="D1" s="5"/>
       <c r="E1" s="6"/>
-      <c r="F1" s="85" t="s">
+      <c r="F1" s="86" t="s">
         <v>38</v>
       </c>
-      <c r="G1" s="86"/>
-      <c r="H1" s="87"/>
-      <c r="I1" s="88" t="s">
+      <c r="G1" s="87"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="89" t="s">
         <v>42</v>
       </c>
       <c r="J1" s="10"/>
@@ -9530,21 +9533,21 @@
       <c r="H4" s="6"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="89" t="s">
+      <c r="A5" s="90" t="s">
         <v>48</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="6"/>
-      <c r="F5" s="90" t="s">
+      <c r="F5" s="91" t="s">
         <v>350</v>
       </c>
-      <c r="G5" s="91"/>
-      <c r="H5" s="92"/>
+      <c r="G5" s="92"/>
+      <c r="H5" s="93"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="93"/>
+      <c r="A6" s="94"/>
       <c r="B6" s="15"/>
       <c r="C6" s="15"/>
       <c r="D6" s="15"/>
@@ -9554,13 +9557,13 @@
       <c r="H6" s="16"/>
     </row>
     <row r="7" ht="21.0" customHeight="1">
-      <c r="A7" s="38" t="s">
+      <c r="A7" s="39" t="s">
         <v>351</v>
       </c>
-      <c r="B7" s="38" t="s">
+      <c r="B7" s="39" t="s">
         <v>352</v>
       </c>
-      <c r="C7" s="38" t="s">
+      <c r="C7" s="39" t="s">
         <v>353</v>
       </c>
       <c r="D7" s="20" t="s">
@@ -9610,26 +9613,26 @@
       </c>
     </row>
     <row r="8" ht="21.75" customHeight="1">
-      <c r="A8" s="94">
+      <c r="A8" s="95">
         <v>1.0</v>
       </c>
-      <c r="B8" s="94" t="s">
+      <c r="B8" s="95" t="s">
         <v>67</v>
       </c>
-      <c r="C8" s="94" t="s">
+      <c r="C8" s="95" t="s">
         <v>67</v>
       </c>
-      <c r="D8" s="95" t="s">
+      <c r="D8" s="96" t="s">
         <v>68</v>
       </c>
-      <c r="E8" s="96" t="s">
+      <c r="E8" s="97" t="s">
         <v>354</v>
       </c>
-      <c r="F8" s="96" t="s">
+      <c r="F8" s="97" t="s">
         <v>355</v>
       </c>
-      <c r="G8" s="40"/>
-      <c r="H8" s="97" t="s">
+      <c r="G8" s="41"/>
+      <c r="H8" s="98" t="s">
         <v>71</v>
       </c>
       <c r="I8" s="28"/>
@@ -9647,26 +9650,26 @@
       </c>
     </row>
     <row r="9" ht="21.0" customHeight="1">
-      <c r="A9" s="94">
+      <c r="A9" s="95">
         <v>2.0</v>
       </c>
-      <c r="B9" s="94" t="s">
+      <c r="B9" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="C9" s="94" t="s">
+      <c r="C9" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="D9" s="95" t="s">
+      <c r="D9" s="96" t="s">
         <v>76</v>
       </c>
-      <c r="E9" s="96" t="s">
+      <c r="E9" s="97" t="s">
         <v>356</v>
       </c>
-      <c r="F9" s="96" t="s">
+      <c r="F9" s="97" t="s">
         <v>357</v>
       </c>
-      <c r="G9" s="40"/>
-      <c r="H9" s="97" t="s">
+      <c r="G9" s="41"/>
+      <c r="H9" s="98" t="s">
         <v>71</v>
       </c>
       <c r="I9" s="31"/>
@@ -9684,26 +9687,26 @@
       </c>
     </row>
     <row r="10" ht="21.75" customHeight="1">
-      <c r="A10" s="94">
+      <c r="A10" s="95">
         <v>3.0</v>
       </c>
-      <c r="B10" s="94" t="s">
+      <c r="B10" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="C10" s="94" t="s">
+      <c r="C10" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="D10" s="95" t="s">
+      <c r="D10" s="96" t="s">
         <v>76</v>
       </c>
-      <c r="E10" s="98" t="s">
+      <c r="E10" s="99" t="s">
         <v>358</v>
       </c>
-      <c r="F10" s="98" t="s">
+      <c r="F10" s="99" t="s">
         <v>359</v>
       </c>
-      <c r="G10" s="40"/>
-      <c r="H10" s="97" t="s">
+      <c r="G10" s="41"/>
+      <c r="H10" s="98" t="s">
         <v>71</v>
       </c>
       <c r="I10" s="31"/>
@@ -9721,26 +9724,26 @@
       </c>
     </row>
     <row r="11" ht="21.0" customHeight="1">
-      <c r="A11" s="94">
+      <c r="A11" s="95">
         <v>4.0</v>
       </c>
-      <c r="B11" s="94" t="s">
+      <c r="B11" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="C11" s="94" t="s">
+      <c r="C11" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="D11" s="95" t="s">
+      <c r="D11" s="96" t="s">
         <v>76</v>
       </c>
-      <c r="E11" s="96" t="s">
+      <c r="E11" s="97" t="s">
         <v>360</v>
       </c>
-      <c r="F11" s="96" t="s">
+      <c r="F11" s="97" t="s">
         <v>361</v>
       </c>
-      <c r="G11" s="40"/>
-      <c r="H11" s="97" t="s">
+      <c r="G11" s="41"/>
+      <c r="H11" s="98" t="s">
         <v>71</v>
       </c>
       <c r="I11" s="31"/>
@@ -9758,26 +9761,26 @@
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1">
-      <c r="A12" s="94">
+      <c r="A12" s="95">
         <v>5.0</v>
       </c>
-      <c r="B12" s="94" t="s">
+      <c r="B12" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="94" t="s">
+      <c r="C12" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="D12" s="95" t="s">
+      <c r="D12" s="96" t="s">
         <v>76</v>
       </c>
-      <c r="E12" s="96" t="s">
+      <c r="E12" s="97" t="s">
         <v>362</v>
       </c>
-      <c r="F12" s="96" t="s">
+      <c r="F12" s="97" t="s">
         <v>355</v>
       </c>
-      <c r="G12" s="40"/>
-      <c r="H12" s="97" t="s">
+      <c r="G12" s="41"/>
+      <c r="H12" s="98" t="s">
         <v>71</v>
       </c>
       <c r="I12" s="28"/>
@@ -9795,26 +9798,26 @@
       </c>
     </row>
     <row r="13" ht="21.75" customHeight="1">
-      <c r="A13" s="94">
+      <c r="A13" s="95">
         <v>6.0</v>
       </c>
-      <c r="B13" s="94" t="s">
+      <c r="B13" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="C13" s="94" t="s">
+      <c r="C13" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="D13" s="95" t="s">
+      <c r="D13" s="96" t="s">
         <v>86</v>
       </c>
-      <c r="E13" s="99" t="s">
+      <c r="E13" s="100" t="s">
         <v>363</v>
       </c>
-      <c r="F13" s="99" t="s">
+      <c r="F13" s="100" t="s">
         <v>185</v>
       </c>
-      <c r="G13" s="40"/>
-      <c r="H13" s="97" t="s">
+      <c r="G13" s="41"/>
+      <c r="H13" s="98" t="s">
         <v>71</v>
       </c>
       <c r="I13" s="31"/>
@@ -9832,26 +9835,26 @@
       </c>
     </row>
     <row r="14" ht="24.75" customHeight="1">
-      <c r="A14" s="94">
+      <c r="A14" s="95">
         <v>7.0</v>
       </c>
-      <c r="B14" s="94" t="s">
+      <c r="B14" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="C14" s="94" t="s">
+      <c r="C14" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="D14" s="95" t="s">
+      <c r="D14" s="96" t="s">
         <v>86</v>
       </c>
-      <c r="E14" s="96" t="s">
+      <c r="E14" s="97" t="s">
         <v>364</v>
       </c>
-      <c r="F14" s="96" t="s">
+      <c r="F14" s="97" t="s">
         <v>181</v>
       </c>
-      <c r="G14" s="40"/>
-      <c r="H14" s="97" t="s">
+      <c r="G14" s="41"/>
+      <c r="H14" s="98" t="s">
         <v>71</v>
       </c>
       <c r="I14" s="28"/>
@@ -9869,26 +9872,26 @@
       </c>
     </row>
     <row r="15" ht="21.0" customHeight="1">
-      <c r="A15" s="94">
+      <c r="A15" s="95">
         <v>8.0</v>
       </c>
-      <c r="B15" s="94" t="s">
+      <c r="B15" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="C15" s="94" t="s">
+      <c r="C15" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="D15" s="95" t="s">
+      <c r="D15" s="96" t="s">
         <v>86</v>
       </c>
-      <c r="E15" s="99" t="s">
+      <c r="E15" s="100" t="s">
         <v>365</v>
       </c>
-      <c r="F15" s="99" t="s">
+      <c r="F15" s="100" t="s">
         <v>366</v>
       </c>
-      <c r="G15" s="40"/>
-      <c r="H15" s="97" t="s">
+      <c r="G15" s="41"/>
+      <c r="H15" s="98" t="s">
         <v>71</v>
       </c>
       <c r="I15" s="31"/>
@@ -9906,26 +9909,26 @@
       </c>
     </row>
     <row r="16" ht="24.75" customHeight="1">
-      <c r="A16" s="94">
+      <c r="A16" s="95">
         <v>9.0</v>
       </c>
-      <c r="B16" s="94" t="s">
+      <c r="B16" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="C16" s="94" t="s">
+      <c r="C16" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="D16" s="95" t="s">
+      <c r="D16" s="96" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="96" t="s">
+      <c r="E16" s="97" t="s">
         <v>367</v>
       </c>
-      <c r="F16" s="96" t="s">
+      <c r="F16" s="97" t="s">
         <v>368</v>
       </c>
-      <c r="G16" s="40"/>
-      <c r="H16" s="97" t="s">
+      <c r="G16" s="41"/>
+      <c r="H16" s="98" t="s">
         <v>71</v>
       </c>
       <c r="I16" s="28"/>
@@ -9943,26 +9946,26 @@
       </c>
     </row>
     <row r="17" ht="27.75" customHeight="1">
-      <c r="A17" s="94">
+      <c r="A17" s="95">
         <v>10.0</v>
       </c>
-      <c r="B17" s="94" t="s">
+      <c r="B17" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="C17" s="94" t="s">
+      <c r="C17" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="D17" s="95" t="s">
+      <c r="D17" s="96" t="s">
         <v>86</v>
       </c>
-      <c r="E17" s="96" t="s">
+      <c r="E17" s="97" t="s">
         <v>369</v>
       </c>
-      <c r="F17" s="96" t="s">
+      <c r="F17" s="97" t="s">
         <v>370</v>
       </c>
-      <c r="G17" s="40"/>
-      <c r="H17" s="97" t="s">
+      <c r="G17" s="41"/>
+      <c r="H17" s="98" t="s">
         <v>71</v>
       </c>
       <c r="I17" s="31"/>
@@ -9980,26 +9983,26 @@
       </c>
     </row>
     <row r="18" ht="20.25" customHeight="1">
-      <c r="A18" s="94">
+      <c r="A18" s="95">
         <v>11.0</v>
       </c>
-      <c r="B18" s="94" t="s">
+      <c r="B18" s="95" t="s">
         <v>121</v>
       </c>
-      <c r="C18" s="94" t="s">
+      <c r="C18" s="95" t="s">
         <v>67</v>
       </c>
-      <c r="D18" s="95" t="s">
+      <c r="D18" s="96" t="s">
         <v>94</v>
       </c>
-      <c r="E18" s="96" t="s">
+      <c r="E18" s="97" t="s">
         <v>371</v>
       </c>
-      <c r="F18" s="96" t="s">
+      <c r="F18" s="97" t="s">
         <v>372</v>
       </c>
-      <c r="G18" s="40"/>
-      <c r="H18" s="97" t="s">
+      <c r="G18" s="41"/>
+      <c r="H18" s="98" t="s">
         <v>71</v>
       </c>
       <c r="I18" s="28"/>
@@ -10017,26 +10020,26 @@
       </c>
     </row>
     <row r="19" ht="21.75" customHeight="1">
-      <c r="A19" s="94">
+      <c r="A19" s="95">
         <v>12.0</v>
       </c>
-      <c r="B19" s="94" t="s">
+      <c r="B19" s="95" t="s">
         <v>121</v>
       </c>
-      <c r="C19" s="94" t="s">
+      <c r="C19" s="95" t="s">
         <v>67</v>
       </c>
-      <c r="D19" s="95" t="s">
+      <c r="D19" s="96" t="s">
         <v>94</v>
       </c>
-      <c r="E19" s="96" t="s">
+      <c r="E19" s="97" t="s">
         <v>373</v>
       </c>
-      <c r="F19" s="96" t="s">
+      <c r="F19" s="97" t="s">
         <v>374</v>
       </c>
-      <c r="G19" s="40"/>
-      <c r="H19" s="97" t="s">
+      <c r="G19" s="41"/>
+      <c r="H19" s="98" t="s">
         <v>71</v>
       </c>
       <c r="I19" s="31"/>
@@ -10054,26 +10057,26 @@
       </c>
     </row>
     <row r="20" ht="21.75" customHeight="1">
-      <c r="A20" s="94">
+      <c r="A20" s="95">
         <v>13.0</v>
       </c>
-      <c r="B20" s="94" t="s">
+      <c r="B20" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="C20" s="94" t="s">
+      <c r="C20" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="D20" s="95" t="s">
+      <c r="D20" s="96" t="s">
         <v>76</v>
       </c>
-      <c r="E20" s="96" t="s">
+      <c r="E20" s="97" t="s">
         <v>375</v>
       </c>
-      <c r="F20" s="96" t="s">
+      <c r="F20" s="97" t="s">
         <v>376</v>
       </c>
-      <c r="G20" s="40"/>
-      <c r="H20" s="97" t="s">
+      <c r="G20" s="41"/>
+      <c r="H20" s="98" t="s">
         <v>71</v>
       </c>
       <c r="I20" s="28"/>
@@ -10091,26 +10094,26 @@
       </c>
     </row>
     <row r="21" ht="22.5" customHeight="1">
-      <c r="A21" s="94">
+      <c r="A21" s="95">
         <v>14.0</v>
       </c>
-      <c r="B21" s="94" t="s">
+      <c r="B21" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="C21" s="94" t="s">
+      <c r="C21" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="D21" s="95" t="s">
+      <c r="D21" s="96" t="s">
         <v>86</v>
       </c>
-      <c r="E21" s="96" t="s">
+      <c r="E21" s="97" t="s">
         <v>377</v>
       </c>
-      <c r="F21" s="96" t="s">
+      <c r="F21" s="97" t="s">
         <v>147</v>
       </c>
-      <c r="G21" s="40"/>
-      <c r="H21" s="97" t="s">
+      <c r="G21" s="41"/>
+      <c r="H21" s="98" t="s">
         <v>71</v>
       </c>
       <c r="I21" s="31"/>
@@ -10128,26 +10131,26 @@
       </c>
     </row>
     <row r="22" ht="23.25" customHeight="1">
-      <c r="A22" s="94">
+      <c r="A22" s="95">
         <v>15.0</v>
       </c>
-      <c r="B22" s="94" t="s">
+      <c r="B22" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="C22" s="94" t="s">
+      <c r="C22" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="D22" s="95" t="s">
+      <c r="D22" s="96" t="s">
         <v>76</v>
       </c>
-      <c r="E22" s="96" t="s">
+      <c r="E22" s="97" t="s">
         <v>378</v>
       </c>
-      <c r="F22" s="96" t="s">
+      <c r="F22" s="97" t="s">
         <v>379</v>
       </c>
-      <c r="G22" s="40"/>
-      <c r="H22" s="97" t="s">
+      <c r="G22" s="41"/>
+      <c r="H22" s="98" t="s">
         <v>71</v>
       </c>
       <c r="I22" s="28"/>
@@ -10165,26 +10168,26 @@
       </c>
     </row>
     <row r="23" ht="21.75" customHeight="1">
-      <c r="A23" s="94">
+      <c r="A23" s="95">
         <v>16.0</v>
       </c>
-      <c r="B23" s="94" t="s">
+      <c r="B23" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="C23" s="94" t="s">
+      <c r="C23" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="D23" s="95" t="s">
+      <c r="D23" s="96" t="s">
         <v>94</v>
       </c>
-      <c r="E23" s="96" t="s">
+      <c r="E23" s="97" t="s">
         <v>380</v>
       </c>
-      <c r="F23" s="96" t="s">
+      <c r="F23" s="97" t="s">
         <v>381</v>
       </c>
-      <c r="G23" s="40"/>
-      <c r="H23" s="100" t="s">
+      <c r="G23" s="41"/>
+      <c r="H23" s="101" t="s">
         <v>71</v>
       </c>
       <c r="I23" s="31"/>
@@ -10202,26 +10205,26 @@
       </c>
     </row>
     <row r="24" ht="21.75" customHeight="1">
-      <c r="A24" s="94">
+      <c r="A24" s="95">
         <v>17.0</v>
       </c>
-      <c r="B24" s="94" t="s">
+      <c r="B24" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="94" t="s">
+      <c r="C24" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="D24" s="95" t="s">
+      <c r="D24" s="96" t="s">
         <v>76</v>
       </c>
-      <c r="E24" s="96" t="s">
+      <c r="E24" s="97" t="s">
         <v>382</v>
       </c>
-      <c r="F24" s="96" t="s">
+      <c r="F24" s="97" t="s">
         <v>383</v>
       </c>
-      <c r="G24" s="40"/>
-      <c r="H24" s="97" t="s">
+      <c r="G24" s="41"/>
+      <c r="H24" s="98" t="s">
         <v>71</v>
       </c>
       <c r="I24" s="31"/>
@@ -10239,26 +10242,26 @@
       </c>
     </row>
     <row r="25" ht="18.75" customHeight="1">
-      <c r="A25" s="94">
+      <c r="A25" s="95">
         <v>18.0</v>
       </c>
-      <c r="B25" s="94" t="s">
+      <c r="B25" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="C25" s="94" t="s">
+      <c r="C25" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="D25" s="95" t="s">
+      <c r="D25" s="96" t="s">
         <v>94</v>
       </c>
-      <c r="E25" s="96" t="s">
+      <c r="E25" s="97" t="s">
         <v>384</v>
       </c>
-      <c r="F25" s="96" t="s">
+      <c r="F25" s="97" t="s">
         <v>385</v>
       </c>
-      <c r="G25" s="40"/>
-      <c r="H25" s="97" t="s">
+      <c r="G25" s="41"/>
+      <c r="H25" s="98" t="s">
         <v>71</v>
       </c>
       <c r="I25" s="28"/>
@@ -10276,26 +10279,26 @@
       </c>
     </row>
     <row r="26" ht="24.0" customHeight="1">
-      <c r="A26" s="94">
+      <c r="A26" s="95">
         <v>19.0</v>
       </c>
-      <c r="B26" s="94" t="s">
+      <c r="B26" s="95" t="s">
         <v>67</v>
       </c>
-      <c r="C26" s="94" t="s">
+      <c r="C26" s="95" t="s">
         <v>67</v>
       </c>
-      <c r="D26" s="95" t="s">
+      <c r="D26" s="96" t="s">
         <v>94</v>
       </c>
-      <c r="E26" s="96" t="s">
+      <c r="E26" s="97" t="s">
         <v>386</v>
       </c>
-      <c r="F26" s="96" t="s">
+      <c r="F26" s="97" t="s">
         <v>387</v>
       </c>
-      <c r="G26" s="40"/>
-      <c r="H26" s="97" t="s">
+      <c r="G26" s="41"/>
+      <c r="H26" s="98" t="s">
         <v>71</v>
       </c>
       <c r="I26" s="28"/>
@@ -10313,26 +10316,26 @@
       </c>
     </row>
     <row r="27" ht="21.75" customHeight="1">
-      <c r="A27" s="94">
+      <c r="A27" s="95">
         <v>20.0</v>
       </c>
-      <c r="B27" s="94" t="s">
+      <c r="B27" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="C27" s="94" t="s">
+      <c r="C27" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="D27" s="95" t="s">
+      <c r="D27" s="96" t="s">
         <v>76</v>
       </c>
-      <c r="E27" s="96" t="s">
+      <c r="E27" s="97" t="s">
         <v>388</v>
       </c>
-      <c r="F27" s="96" t="s">
+      <c r="F27" s="97" t="s">
         <v>361</v>
       </c>
-      <c r="G27" s="40"/>
-      <c r="H27" s="97" t="s">
+      <c r="G27" s="41"/>
+      <c r="H27" s="98" t="s">
         <v>71</v>
       </c>
       <c r="I27" s="28"/>
@@ -10350,26 +10353,26 @@
       </c>
     </row>
     <row r="28" ht="20.25" customHeight="1">
-      <c r="A28" s="94">
+      <c r="A28" s="95">
         <v>21.0</v>
       </c>
-      <c r="B28" s="94" t="s">
+      <c r="B28" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="C28" s="94" t="s">
+      <c r="C28" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="D28" s="95" t="s">
+      <c r="D28" s="96" t="s">
         <v>94</v>
       </c>
-      <c r="E28" s="96" t="s">
+      <c r="E28" s="97" t="s">
         <v>389</v>
       </c>
-      <c r="F28" s="96" t="s">
+      <c r="F28" s="97" t="s">
         <v>390</v>
       </c>
-      <c r="G28" s="40"/>
-      <c r="H28" s="97" t="s">
+      <c r="G28" s="41"/>
+      <c r="H28" s="98" t="s">
         <v>99</v>
       </c>
       <c r="I28" s="31"/>
@@ -10387,26 +10390,26 @@
       </c>
     </row>
     <row r="29" ht="19.5" customHeight="1">
-      <c r="A29" s="94">
+      <c r="A29" s="95">
         <v>22.0</v>
       </c>
-      <c r="B29" s="94" t="s">
+      <c r="B29" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="C29" s="94" t="s">
+      <c r="C29" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="D29" s="95" t="s">
+      <c r="D29" s="96" t="s">
         <v>86</v>
       </c>
-      <c r="E29" s="96" t="s">
+      <c r="E29" s="97" t="s">
         <v>391</v>
       </c>
-      <c r="F29" s="96" t="s">
+      <c r="F29" s="97" t="s">
         <v>392</v>
       </c>
-      <c r="G29" s="40"/>
-      <c r="H29" s="97" t="s">
+      <c r="G29" s="41"/>
+      <c r="H29" s="98" t="s">
         <v>71</v>
       </c>
       <c r="I29" s="28"/>
@@ -10424,26 +10427,26 @@
       </c>
     </row>
     <row r="30" ht="20.25" customHeight="1">
-      <c r="A30" s="94">
+      <c r="A30" s="95">
         <v>23.0</v>
       </c>
-      <c r="B30" s="94" t="s">
+      <c r="B30" s="95" t="s">
         <v>121</v>
       </c>
-      <c r="C30" s="94" t="s">
+      <c r="C30" s="95" t="s">
         <v>67</v>
       </c>
-      <c r="D30" s="95" t="s">
+      <c r="D30" s="96" t="s">
         <v>94</v>
       </c>
-      <c r="E30" s="96" t="s">
+      <c r="E30" s="97" t="s">
         <v>393</v>
       </c>
-      <c r="F30" s="96" t="s">
+      <c r="F30" s="97" t="s">
         <v>394</v>
       </c>
-      <c r="G30" s="40"/>
-      <c r="H30" s="97" t="s">
+      <c r="G30" s="41"/>
+      <c r="H30" s="98" t="s">
         <v>71</v>
       </c>
       <c r="I30" s="31"/>
@@ -10461,26 +10464,26 @@
       </c>
     </row>
     <row r="31" ht="21.0" customHeight="1">
-      <c r="A31" s="94">
+      <c r="A31" s="95">
         <v>24.0</v>
       </c>
-      <c r="B31" s="94" t="s">
+      <c r="B31" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="C31" s="94" t="s">
+      <c r="C31" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="D31" s="95" t="s">
+      <c r="D31" s="96" t="s">
         <v>86</v>
       </c>
-      <c r="E31" s="96" t="s">
+      <c r="E31" s="97" t="s">
         <v>395</v>
       </c>
-      <c r="F31" s="96" t="s">
+      <c r="F31" s="97" t="s">
         <v>396</v>
       </c>
-      <c r="G31" s="40"/>
-      <c r="H31" s="97" t="s">
+      <c r="G31" s="41"/>
+      <c r="H31" s="98" t="s">
         <v>71</v>
       </c>
       <c r="I31" s="28"/>
@@ -10498,26 +10501,26 @@
       </c>
     </row>
     <row r="32" ht="22.5" customHeight="1">
-      <c r="A32" s="94">
+      <c r="A32" s="95">
         <v>25.0</v>
       </c>
-      <c r="B32" s="94" t="s">
+      <c r="B32" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="C32" s="94" t="s">
+      <c r="C32" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="D32" s="95" t="s">
+      <c r="D32" s="96" t="s">
         <v>86</v>
       </c>
-      <c r="E32" s="96" t="s">
+      <c r="E32" s="97" t="s">
         <v>397</v>
       </c>
-      <c r="F32" s="96" t="s">
+      <c r="F32" s="97" t="s">
         <v>398</v>
       </c>
-      <c r="G32" s="40"/>
-      <c r="H32" s="97" t="s">
+      <c r="G32" s="41"/>
+      <c r="H32" s="98" t="s">
         <v>71</v>
       </c>
       <c r="I32" s="31"/>
@@ -10535,26 +10538,26 @@
       </c>
     </row>
     <row r="33" ht="21.0" customHeight="1">
-      <c r="A33" s="94">
+      <c r="A33" s="95">
         <v>26.0</v>
       </c>
-      <c r="B33" s="94" t="s">
+      <c r="B33" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="C33" s="94" t="s">
+      <c r="C33" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="D33" s="95" t="s">
+      <c r="D33" s="96" t="s">
         <v>86</v>
       </c>
-      <c r="E33" s="96" t="s">
+      <c r="E33" s="97" t="s">
         <v>87</v>
       </c>
-      <c r="F33" s="96" t="s">
+      <c r="F33" s="97" t="s">
         <v>399</v>
       </c>
-      <c r="G33" s="40"/>
-      <c r="H33" s="97" t="s">
+      <c r="G33" s="41"/>
+      <c r="H33" s="98" t="s">
         <v>400</v>
       </c>
       <c r="I33" s="28"/>
@@ -10717,10 +10720,10 @@
       <c r="H6" s="13"/>
     </row>
     <row r="7" ht="21.0" customHeight="1">
-      <c r="A7" s="38" t="s">
+      <c r="A7" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="38" t="s">
+      <c r="B7" s="39" t="s">
         <v>51</v>
       </c>
       <c r="C7" s="20" t="s">
@@ -10770,23 +10773,23 @@
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="48">
+      <c r="A8" s="49">
         <v>3.0</v>
       </c>
       <c r="B8" s="23" t="s">
         <v>121</v>
       </c>
-      <c r="C8" s="101" t="s">
+      <c r="C8" s="102" t="s">
         <v>76</v>
       </c>
-      <c r="D8" s="45" t="s">
+      <c r="D8" s="46" t="s">
         <v>306</v>
       </c>
-      <c r="E8" s="45" t="s">
+      <c r="E8" s="46" t="s">
         <v>406</v>
       </c>
-      <c r="F8" s="40"/>
-      <c r="G8" s="41" t="s">
+      <c r="F8" s="41"/>
+      <c r="G8" s="42" t="s">
         <v>85</v>
       </c>
       <c r="H8" s="28"/>
@@ -10819,8 +10822,8 @@
       <c r="E9" s="23" t="s">
         <v>408</v>
       </c>
-      <c r="F9" s="40"/>
-      <c r="G9" s="41" t="s">
+      <c r="F9" s="41"/>
+      <c r="G9" s="42" t="s">
         <v>409</v>
       </c>
       <c r="H9" s="31"/>
@@ -10838,7 +10841,7 @@
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="48">
+      <c r="A10" s="49">
         <v>1.0</v>
       </c>
       <c r="B10" s="23" t="s">
@@ -10853,8 +10856,8 @@
       <c r="E10" s="23" t="s">
         <v>411</v>
       </c>
-      <c r="F10" s="40"/>
-      <c r="G10" s="41" t="s">
+      <c r="F10" s="41"/>
+      <c r="G10" s="42" t="s">
         <v>412</v>
       </c>
       <c r="H10" s="28"/>
@@ -10887,8 +10890,8 @@
       <c r="E11" s="23" t="s">
         <v>414</v>
       </c>
-      <c r="F11" s="40"/>
-      <c r="G11" s="41" t="s">
+      <c r="F11" s="41"/>
+      <c r="G11" s="42" t="s">
         <v>401</v>
       </c>
       <c r="H11" s="31"/>
@@ -10921,8 +10924,8 @@
       <c r="E12" s="23" t="s">
         <v>416</v>
       </c>
-      <c r="F12" s="40"/>
-      <c r="G12" s="41" t="s">
+      <c r="F12" s="41"/>
+      <c r="G12" s="42" t="s">
         <v>401</v>
       </c>
       <c r="H12" s="28"/>
@@ -10955,8 +10958,8 @@
       <c r="E13" s="23" t="s">
         <v>418</v>
       </c>
-      <c r="F13" s="40"/>
-      <c r="G13" s="41" t="s">
+      <c r="F13" s="41"/>
+      <c r="G13" s="42" t="s">
         <v>401</v>
       </c>
       <c r="H13" s="31"/>
@@ -10989,8 +10992,8 @@
       <c r="E14" s="23" t="s">
         <v>269</v>
       </c>
-      <c r="F14" s="40"/>
-      <c r="G14" s="41" t="s">
+      <c r="F14" s="41"/>
+      <c r="G14" s="42" t="s">
         <v>75</v>
       </c>
       <c r="H14" s="28"/>
@@ -11023,8 +11026,8 @@
       <c r="E15" s="23" t="s">
         <v>421</v>
       </c>
-      <c r="F15" s="40"/>
-      <c r="G15" s="41" t="s">
+      <c r="F15" s="41"/>
+      <c r="G15" s="42" t="s">
         <v>71</v>
       </c>
       <c r="H15" s="31"/>
@@ -11057,8 +11060,8 @@
       <c r="E16" s="23" t="s">
         <v>423</v>
       </c>
-      <c r="F16" s="40"/>
-      <c r="G16" s="41" t="s">
+      <c r="F16" s="41"/>
+      <c r="G16" s="42" t="s">
         <v>294</v>
       </c>
       <c r="H16" s="28"/>
@@ -11091,8 +11094,8 @@
       <c r="E17" s="23" t="s">
         <v>425</v>
       </c>
-      <c r="F17" s="40"/>
-      <c r="G17" s="41" t="s">
+      <c r="F17" s="41"/>
+      <c r="G17" s="42" t="s">
         <v>401</v>
       </c>
       <c r="H17" s="31"/>
@@ -11125,20 +11128,20 @@
       <c r="E18" s="23" t="s">
         <v>427</v>
       </c>
-      <c r="F18" s="102"/>
-      <c r="G18" s="103" t="s">
+      <c r="F18" s="103"/>
+      <c r="G18" s="104" t="s">
         <v>428</v>
       </c>
-      <c r="H18" s="66"/>
-      <c r="I18" s="104"/>
-      <c r="J18" s="104"/>
-      <c r="K18" s="104"/>
-      <c r="L18" s="104"/>
-      <c r="M18" s="104"/>
-      <c r="N18" s="104"/>
-      <c r="O18" s="104"/>
-      <c r="P18" s="104"/>
-      <c r="Q18" s="66">
+      <c r="H18" s="67"/>
+      <c r="I18" s="105"/>
+      <c r="J18" s="105"/>
+      <c r="K18" s="105"/>
+      <c r="L18" s="105"/>
+      <c r="M18" s="105"/>
+      <c r="N18" s="105"/>
+      <c r="O18" s="105"/>
+      <c r="P18" s="105"/>
+      <c r="Q18" s="67">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11159,20 +11162,20 @@
       <c r="E19" s="23" t="s">
         <v>430</v>
       </c>
-      <c r="F19" s="102"/>
-      <c r="G19" s="103" t="s">
+      <c r="F19" s="103"/>
+      <c r="G19" s="104" t="s">
         <v>401</v>
       </c>
-      <c r="H19" s="66"/>
-      <c r="I19" s="67"/>
-      <c r="J19" s="67"/>
-      <c r="K19" s="67"/>
-      <c r="L19" s="67"/>
-      <c r="M19" s="67"/>
-      <c r="N19" s="67"/>
-      <c r="O19" s="67"/>
-      <c r="P19" s="67"/>
-      <c r="Q19" s="66">
+      <c r="H19" s="67"/>
+      <c r="I19" s="68"/>
+      <c r="J19" s="68"/>
+      <c r="K19" s="68"/>
+      <c r="L19" s="68"/>
+      <c r="M19" s="68"/>
+      <c r="N19" s="68"/>
+      <c r="O19" s="68"/>
+      <c r="P19" s="68"/>
+      <c r="Q19" s="67">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11193,20 +11196,20 @@
       <c r="E20" s="23" t="s">
         <v>432</v>
       </c>
-      <c r="F20" s="102"/>
-      <c r="G20" s="103" t="s">
+      <c r="F20" s="103"/>
+      <c r="G20" s="104" t="s">
         <v>401</v>
       </c>
-      <c r="H20" s="66"/>
-      <c r="I20" s="104"/>
-      <c r="J20" s="104"/>
-      <c r="K20" s="104"/>
-      <c r="L20" s="104"/>
-      <c r="M20" s="104"/>
-      <c r="N20" s="104"/>
-      <c r="O20" s="104"/>
-      <c r="P20" s="104"/>
-      <c r="Q20" s="66">
+      <c r="H20" s="67"/>
+      <c r="I20" s="105"/>
+      <c r="J20" s="105"/>
+      <c r="K20" s="105"/>
+      <c r="L20" s="105"/>
+      <c r="M20" s="105"/>
+      <c r="N20" s="105"/>
+      <c r="O20" s="105"/>
+      <c r="P20" s="105"/>
+      <c r="Q20" s="67">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11227,10 +11230,10 @@
       <c r="E21" s="23" t="s">
         <v>434</v>
       </c>
-      <c r="F21" s="40">
+      <c r="F21" s="41">
         <v>20.0</v>
       </c>
-      <c r="G21" s="41" t="s">
+      <c r="G21" s="42" t="s">
         <v>435</v>
       </c>
       <c r="H21" s="31"/>
@@ -11263,8 +11266,8 @@
       <c r="E22" s="23" t="s">
         <v>437</v>
       </c>
-      <c r="F22" s="40"/>
-      <c r="G22" s="41" t="s">
+      <c r="F22" s="41"/>
+      <c r="G22" s="42" t="s">
         <v>309</v>
       </c>
       <c r="H22" s="28"/>
@@ -11297,18 +11300,18 @@
       <c r="E23" s="23" t="s">
         <v>439</v>
       </c>
-      <c r="F23" s="102"/>
-      <c r="G23" s="103"/>
-      <c r="H23" s="66"/>
-      <c r="I23" s="104"/>
-      <c r="J23" s="104"/>
-      <c r="K23" s="104"/>
-      <c r="L23" s="104"/>
-      <c r="M23" s="104"/>
-      <c r="N23" s="104"/>
-      <c r="O23" s="104"/>
-      <c r="P23" s="104"/>
-      <c r="Q23" s="66">
+      <c r="F23" s="103"/>
+      <c r="G23" s="104"/>
+      <c r="H23" s="67"/>
+      <c r="I23" s="105"/>
+      <c r="J23" s="105"/>
+      <c r="K23" s="105"/>
+      <c r="L23" s="105"/>
+      <c r="M23" s="105"/>
+      <c r="N23" s="105"/>
+      <c r="O23" s="105"/>
+      <c r="P23" s="105"/>
+      <c r="Q23" s="67">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11329,8 +11332,8 @@
       <c r="E24" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="F24" s="40"/>
-      <c r="G24" s="41" t="s">
+      <c r="F24" s="41"/>
+      <c r="G24" s="42" t="s">
         <v>75</v>
       </c>
       <c r="H24" s="28"/>
@@ -11363,20 +11366,20 @@
       <c r="E25" s="23" t="s">
         <v>406</v>
       </c>
-      <c r="F25" s="102"/>
-      <c r="G25" s="103" t="s">
+      <c r="F25" s="103"/>
+      <c r="G25" s="104" t="s">
         <v>75</v>
       </c>
-      <c r="H25" s="66"/>
-      <c r="I25" s="104"/>
-      <c r="J25" s="104"/>
-      <c r="K25" s="104"/>
-      <c r="L25" s="104"/>
-      <c r="M25" s="104"/>
-      <c r="N25" s="104"/>
-      <c r="O25" s="104"/>
-      <c r="P25" s="104"/>
-      <c r="Q25" s="66">
+      <c r="H25" s="67"/>
+      <c r="I25" s="105"/>
+      <c r="J25" s="105"/>
+      <c r="K25" s="105"/>
+      <c r="L25" s="105"/>
+      <c r="M25" s="105"/>
+      <c r="N25" s="105"/>
+      <c r="O25" s="105"/>
+      <c r="P25" s="105"/>
+      <c r="Q25" s="67">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11397,8 +11400,8 @@
       <c r="E26" s="23" t="s">
         <v>443</v>
       </c>
-      <c r="F26" s="40"/>
-      <c r="G26" s="41" t="s">
+      <c r="F26" s="41"/>
+      <c r="G26" s="42" t="s">
         <v>99</v>
       </c>
       <c r="H26" s="28"/>
@@ -11431,8 +11434,8 @@
       <c r="E27" s="23" t="s">
         <v>445</v>
       </c>
-      <c r="F27" s="40"/>
-      <c r="G27" s="41" t="s">
+      <c r="F27" s="41"/>
+      <c r="G27" s="42" t="s">
         <v>401</v>
       </c>
       <c r="H27" s="31"/>
@@ -11465,8 +11468,8 @@
       <c r="E28" s="23" t="s">
         <v>447</v>
       </c>
-      <c r="F28" s="40"/>
-      <c r="G28" s="41"/>
+      <c r="F28" s="41"/>
+      <c r="G28" s="42"/>
       <c r="H28" s="28"/>
       <c r="I28" s="29"/>
       <c r="J28" s="29"/>
@@ -11497,8 +11500,8 @@
       <c r="E29" s="23" t="s">
         <v>449</v>
       </c>
-      <c r="F29" s="40"/>
-      <c r="G29" s="41" t="s">
+      <c r="F29" s="41"/>
+      <c r="G29" s="42" t="s">
         <v>401</v>
       </c>
       <c r="H29" s="31"/>
@@ -11531,8 +11534,8 @@
       <c r="E30" s="23" t="s">
         <v>451</v>
       </c>
-      <c r="F30" s="40"/>
-      <c r="G30" s="41" t="s">
+      <c r="F30" s="41"/>
+      <c r="G30" s="42" t="s">
         <v>452</v>
       </c>
       <c r="H30" s="28"/>
@@ -11565,52 +11568,52 @@
       <c r="E31" s="23" t="s">
         <v>430</v>
       </c>
-      <c r="F31" s="102"/>
-      <c r="G31" s="103" t="s">
+      <c r="F31" s="103"/>
+      <c r="G31" s="104" t="s">
         <v>401</v>
       </c>
-      <c r="H31" s="66"/>
-      <c r="I31" s="104"/>
-      <c r="J31" s="104"/>
-      <c r="K31" s="104"/>
-      <c r="L31" s="104"/>
-      <c r="M31" s="104"/>
-      <c r="N31" s="104"/>
-      <c r="O31" s="104"/>
-      <c r="P31" s="104"/>
-      <c r="Q31" s="66">
+      <c r="H31" s="67"/>
+      <c r="I31" s="105"/>
+      <c r="J31" s="105"/>
+      <c r="K31" s="105"/>
+      <c r="L31" s="105"/>
+      <c r="M31" s="105"/>
+      <c r="N31" s="105"/>
+      <c r="O31" s="105"/>
+      <c r="P31" s="105"/>
+      <c r="Q31" s="67">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="105">
+      <c r="A32" s="106">
         <v>25.0</v>
       </c>
-      <c r="B32" s="106" t="s">
+      <c r="B32" s="107" t="s">
         <v>67</v>
       </c>
-      <c r="C32" s="107" t="s">
+      <c r="C32" s="108" t="s">
         <v>94</v>
       </c>
-      <c r="D32" s="106" t="s">
+      <c r="D32" s="107" t="s">
         <v>454</v>
       </c>
-      <c r="E32" s="106" t="s">
+      <c r="E32" s="107" t="s">
         <v>455</v>
       </c>
-      <c r="F32" s="102"/>
-      <c r="G32" s="103"/>
-      <c r="H32" s="66"/>
-      <c r="I32" s="104"/>
-      <c r="J32" s="104"/>
-      <c r="K32" s="104"/>
-      <c r="L32" s="104"/>
-      <c r="M32" s="104"/>
-      <c r="N32" s="104"/>
-      <c r="O32" s="104"/>
-      <c r="P32" s="104"/>
-      <c r="Q32" s="66">
+      <c r="F32" s="103"/>
+      <c r="G32" s="104"/>
+      <c r="H32" s="67"/>
+      <c r="I32" s="105"/>
+      <c r="J32" s="105"/>
+      <c r="K32" s="105"/>
+      <c r="L32" s="105"/>
+      <c r="M32" s="105"/>
+      <c r="N32" s="105"/>
+      <c r="O32" s="105"/>
+      <c r="P32" s="105"/>
+      <c r="Q32" s="67">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11631,8 +11634,8 @@
       <c r="E33" s="23" t="s">
         <v>457</v>
       </c>
-      <c r="F33" s="40"/>
-      <c r="G33" s="41" t="s">
+      <c r="F33" s="41"/>
+      <c r="G33" s="42" t="s">
         <v>458</v>
       </c>
       <c r="H33" s="31"/>
@@ -11712,7 +11715,7 @@
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="6"/>
-      <c r="E1" s="108" t="s">
+      <c r="E1" s="109" t="s">
         <v>37</v>
       </c>
       <c r="F1" s="5"/>
@@ -11737,7 +11740,7 @@
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
       <c r="D2" s="6"/>
-      <c r="E2" s="108"/>
+      <c r="E2" s="109"/>
       <c r="F2" s="5"/>
       <c r="G2" s="6"/>
       <c r="H2" s="13"/>
@@ -11749,7 +11752,7 @@
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
       <c r="D3" s="6"/>
-      <c r="E3" s="108" t="s">
+      <c r="E3" s="109" t="s">
         <v>459</v>
       </c>
       <c r="F3" s="5"/>
@@ -11763,7 +11766,7 @@
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
-      <c r="E4" s="109" t="s">
+      <c r="E4" s="110" t="s">
         <v>460</v>
       </c>
       <c r="F4" s="5"/>
@@ -11777,7 +11780,7 @@
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
       <c r="D5" s="6"/>
-      <c r="E5" s="108" t="s">
+      <c r="E5" s="109" t="s">
         <v>461</v>
       </c>
       <c r="F5" s="5"/>
@@ -11795,10 +11798,10 @@
       <c r="H6" s="13"/>
     </row>
     <row r="7" ht="21.0" customHeight="1">
-      <c r="A7" s="38" t="s">
+      <c r="A7" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="38" t="s">
+      <c r="B7" s="39" t="s">
         <v>51</v>
       </c>
       <c r="C7" s="20" t="s">
@@ -11848,23 +11851,23 @@
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="74">
+      <c r="A8" s="75">
         <v>1.0</v>
       </c>
-      <c r="B8" s="110" t="s">
+      <c r="B8" s="111" t="s">
         <v>72</v>
       </c>
-      <c r="C8" s="111" t="s">
+      <c r="C8" s="112" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="112" t="s">
+      <c r="D8" s="113" t="s">
         <v>462</v>
       </c>
-      <c r="E8" s="112" t="s">
+      <c r="E8" s="113" t="s">
         <v>240</v>
       </c>
-      <c r="F8" s="40"/>
-      <c r="G8" s="41"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="42"/>
       <c r="H8" s="28"/>
       <c r="I8" s="29"/>
       <c r="J8" s="29"/>
@@ -11880,23 +11883,23 @@
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="76">
+      <c r="A9" s="77">
         <v>2.0</v>
       </c>
-      <c r="B9" s="110" t="s">
+      <c r="B9" s="111" t="s">
         <v>102</v>
       </c>
-      <c r="C9" s="111" t="s">
+      <c r="C9" s="112" t="s">
         <v>76</v>
       </c>
-      <c r="D9" s="112" t="s">
+      <c r="D9" s="113" t="s">
         <v>463</v>
       </c>
-      <c r="E9" s="112" t="s">
+      <c r="E9" s="113" t="s">
         <v>464</v>
       </c>
-      <c r="F9" s="40"/>
-      <c r="G9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="42"/>
       <c r="H9" s="31"/>
       <c r="I9" s="32"/>
       <c r="J9" s="32"/>
@@ -11912,23 +11915,23 @@
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="74">
+      <c r="A10" s="75">
         <v>3.0</v>
       </c>
-      <c r="B10" s="110" t="s">
+      <c r="B10" s="111" t="s">
         <v>72</v>
       </c>
-      <c r="C10" s="111" t="s">
+      <c r="C10" s="112" t="s">
         <v>86</v>
       </c>
-      <c r="D10" s="113" t="s">
+      <c r="D10" s="114" t="s">
         <v>465</v>
       </c>
-      <c r="E10" s="113" t="s">
+      <c r="E10" s="114" t="s">
         <v>466</v>
       </c>
-      <c r="F10" s="40"/>
-      <c r="G10" s="41"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="42"/>
       <c r="H10" s="28"/>
       <c r="I10" s="29"/>
       <c r="J10" s="29"/>
@@ -11944,23 +11947,23 @@
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="76">
+      <c r="A11" s="77">
         <v>4.0</v>
       </c>
-      <c r="B11" s="110" t="s">
+      <c r="B11" s="111" t="s">
         <v>72</v>
       </c>
-      <c r="C11" s="111" t="s">
+      <c r="C11" s="112" t="s">
         <v>86</v>
       </c>
-      <c r="D11" s="113" t="s">
+      <c r="D11" s="114" t="s">
         <v>467</v>
       </c>
-      <c r="E11" s="113" t="s">
+      <c r="E11" s="114" t="s">
         <v>468</v>
       </c>
-      <c r="F11" s="40"/>
-      <c r="G11" s="41"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="42"/>
       <c r="H11" s="31"/>
       <c r="I11" s="32"/>
       <c r="J11" s="32"/>
@@ -11976,23 +11979,23 @@
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="74">
+      <c r="A12" s="75">
         <v>5.0</v>
       </c>
-      <c r="B12" s="110" t="s">
+      <c r="B12" s="111" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="111" t="s">
+      <c r="C12" s="112" t="s">
         <v>76</v>
       </c>
-      <c r="D12" s="114" t="s">
+      <c r="D12" s="115" t="s">
         <v>469</v>
       </c>
-      <c r="E12" s="112" t="s">
+      <c r="E12" s="113" t="s">
         <v>470</v>
       </c>
-      <c r="F12" s="40"/>
-      <c r="G12" s="41"/>
+      <c r="F12" s="41"/>
+      <c r="G12" s="42"/>
       <c r="H12" s="28"/>
       <c r="I12" s="29"/>
       <c r="J12" s="29"/>
@@ -12008,23 +12011,23 @@
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="76">
+      <c r="A13" s="77">
         <v>6.0</v>
       </c>
-      <c r="B13" s="110" t="s">
+      <c r="B13" s="111" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="115" t="s">
+      <c r="C13" s="116" t="s">
         <v>86</v>
       </c>
-      <c r="D13" s="114" t="s">
+      <c r="D13" s="115" t="s">
         <v>471</v>
       </c>
-      <c r="E13" s="114" t="s">
+      <c r="E13" s="115" t="s">
         <v>472</v>
       </c>
-      <c r="F13" s="40"/>
-      <c r="G13" s="41"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="42"/>
       <c r="H13" s="31"/>
       <c r="I13" s="32"/>
       <c r="J13" s="32"/>
@@ -12040,23 +12043,23 @@
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="74">
+      <c r="A14" s="75">
         <v>7.0</v>
       </c>
-      <c r="B14" s="110" t="s">
+      <c r="B14" s="111" t="s">
         <v>102</v>
       </c>
-      <c r="C14" s="115" t="s">
+      <c r="C14" s="116" t="s">
         <v>94</v>
       </c>
-      <c r="D14" s="114" t="s">
+      <c r="D14" s="115" t="s">
         <v>473</v>
       </c>
-      <c r="E14" s="114" t="s">
+      <c r="E14" s="115" t="s">
         <v>474</v>
       </c>
-      <c r="F14" s="40"/>
-      <c r="G14" s="41"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="42"/>
       <c r="H14" s="28"/>
       <c r="I14" s="29"/>
       <c r="J14" s="29"/>
@@ -12072,23 +12075,23 @@
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="76">
+      <c r="A15" s="77">
         <v>8.0</v>
       </c>
-      <c r="B15" s="110" t="s">
+      <c r="B15" s="111" t="s">
         <v>102</v>
       </c>
-      <c r="C15" s="115" t="s">
+      <c r="C15" s="116" t="s">
         <v>86</v>
       </c>
-      <c r="D15" s="114" t="s">
+      <c r="D15" s="115" t="s">
         <v>475</v>
       </c>
-      <c r="E15" s="114" t="s">
+      <c r="E15" s="115" t="s">
         <v>476</v>
       </c>
-      <c r="F15" s="40"/>
-      <c r="G15" s="41"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="42"/>
       <c r="H15" s="31"/>
       <c r="I15" s="32"/>
       <c r="J15" s="32"/>
@@ -12104,23 +12107,23 @@
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="74">
+      <c r="A16" s="75">
         <v>9.0</v>
       </c>
-      <c r="B16" s="110" t="s">
+      <c r="B16" s="111" t="s">
         <v>72</v>
       </c>
-      <c r="C16" s="115" t="s">
+      <c r="C16" s="116" t="s">
         <v>94</v>
       </c>
-      <c r="D16" s="114" t="s">
+      <c r="D16" s="115" t="s">
         <v>477</v>
       </c>
-      <c r="E16" s="114" t="s">
+      <c r="E16" s="115" t="s">
         <v>478</v>
       </c>
-      <c r="F16" s="40"/>
-      <c r="G16" s="41"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="42"/>
       <c r="H16" s="28"/>
       <c r="I16" s="29"/>
       <c r="J16" s="29"/>
@@ -12136,23 +12139,23 @@
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="76">
+      <c r="A17" s="77">
         <v>10.0</v>
       </c>
-      <c r="B17" s="110" t="s">
+      <c r="B17" s="111" t="s">
         <v>72</v>
       </c>
-      <c r="C17" s="115" t="s">
+      <c r="C17" s="116" t="s">
         <v>94</v>
       </c>
-      <c r="D17" s="116" t="s">
+      <c r="D17" s="117" t="s">
         <v>479</v>
       </c>
-      <c r="E17" s="116" t="s">
+      <c r="E17" s="117" t="s">
         <v>480</v>
       </c>
-      <c r="F17" s="40"/>
-      <c r="G17" s="41"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="42"/>
       <c r="H17" s="31"/>
       <c r="I17" s="32"/>
       <c r="J17" s="32"/>
@@ -12168,23 +12171,23 @@
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="74">
+      <c r="A18" s="75">
         <v>12.0</v>
       </c>
-      <c r="B18" s="110" t="s">
+      <c r="B18" s="111" t="s">
         <v>72</v>
       </c>
-      <c r="C18" s="115" t="s">
+      <c r="C18" s="116" t="s">
         <v>94</v>
       </c>
-      <c r="D18" s="114" t="s">
+      <c r="D18" s="115" t="s">
         <v>481</v>
       </c>
-      <c r="E18" s="114" t="s">
+      <c r="E18" s="115" t="s">
         <v>482</v>
       </c>
-      <c r="F18" s="40"/>
-      <c r="G18" s="41"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="42"/>
       <c r="H18" s="28"/>
       <c r="I18" s="29"/>
       <c r="J18" s="29"/>
@@ -12200,23 +12203,23 @@
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="76">
+      <c r="A19" s="77">
         <v>11.0</v>
       </c>
-      <c r="B19" s="110" t="s">
+      <c r="B19" s="111" t="s">
         <v>72</v>
       </c>
-      <c r="C19" s="115" t="s">
+      <c r="C19" s="116" t="s">
         <v>94</v>
       </c>
-      <c r="D19" s="114" t="s">
+      <c r="D19" s="115" t="s">
         <v>483</v>
       </c>
-      <c r="E19" s="114" t="s">
+      <c r="E19" s="115" t="s">
         <v>484</v>
       </c>
-      <c r="F19" s="40"/>
-      <c r="G19" s="41"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="42"/>
       <c r="H19" s="31"/>
       <c r="I19" s="32"/>
       <c r="J19" s="32"/>
@@ -12232,23 +12235,23 @@
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="74">
+      <c r="A20" s="75">
         <v>13.0</v>
       </c>
-      <c r="B20" s="110" t="s">
+      <c r="B20" s="111" t="s">
         <v>102</v>
       </c>
-      <c r="C20" s="115" t="s">
+      <c r="C20" s="116" t="s">
         <v>94</v>
       </c>
-      <c r="D20" s="114" t="s">
+      <c r="D20" s="115" t="s">
         <v>87</v>
       </c>
-      <c r="E20" s="114" t="s">
+      <c r="E20" s="115" t="s">
         <v>485</v>
       </c>
-      <c r="F20" s="40"/>
-      <c r="G20" s="41"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="42"/>
       <c r="H20" s="28"/>
       <c r="I20" s="29"/>
       <c r="J20" s="29"/>
@@ -12264,23 +12267,23 @@
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="76">
+      <c r="A21" s="77">
         <v>14.0</v>
       </c>
-      <c r="B21" s="110" t="s">
+      <c r="B21" s="111" t="s">
         <v>72</v>
       </c>
-      <c r="C21" s="115" t="s">
+      <c r="C21" s="116" t="s">
         <v>86</v>
       </c>
-      <c r="D21" s="114" t="s">
+      <c r="D21" s="115" t="s">
         <v>473</v>
       </c>
-      <c r="E21" s="114" t="s">
+      <c r="E21" s="115" t="s">
         <v>486</v>
       </c>
-      <c r="F21" s="40"/>
-      <c r="G21" s="41"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="42"/>
       <c r="H21" s="31"/>
       <c r="I21" s="32"/>
       <c r="J21" s="32"/>
@@ -12296,23 +12299,23 @@
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="74">
+      <c r="A22" s="75">
         <v>15.0</v>
       </c>
-      <c r="B22" s="110" t="s">
+      <c r="B22" s="111" t="s">
         <v>72</v>
       </c>
-      <c r="C22" s="111" t="s">
+      <c r="C22" s="112" t="s">
         <v>86</v>
       </c>
-      <c r="D22" s="116" t="s">
+      <c r="D22" s="117" t="s">
         <v>487</v>
       </c>
-      <c r="E22" s="116" t="s">
+      <c r="E22" s="117" t="s">
         <v>374</v>
       </c>
-      <c r="F22" s="40"/>
-      <c r="G22" s="41"/>
+      <c r="F22" s="41"/>
+      <c r="G22" s="42"/>
       <c r="H22" s="28"/>
       <c r="I22" s="29"/>
       <c r="J22" s="29"/>
@@ -12328,23 +12331,23 @@
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="76">
+      <c r="A23" s="77">
         <v>16.0</v>
       </c>
-      <c r="B23" s="110" t="s">
+      <c r="B23" s="111" t="s">
         <v>72</v>
       </c>
-      <c r="C23" s="111" t="s">
+      <c r="C23" s="112" t="s">
         <v>86</v>
       </c>
-      <c r="D23" s="116" t="s">
+      <c r="D23" s="117" t="s">
         <v>488</v>
       </c>
-      <c r="E23" s="116" t="s">
+      <c r="E23" s="117" t="s">
         <v>489</v>
       </c>
-      <c r="F23" s="40"/>
-      <c r="G23" s="41"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="42"/>
       <c r="H23" s="31"/>
       <c r="I23" s="32"/>
       <c r="J23" s="32"/>
@@ -12360,23 +12363,23 @@
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="74">
+      <c r="A24" s="75">
         <v>17.0</v>
       </c>
-      <c r="B24" s="110" t="s">
+      <c r="B24" s="111" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="111" t="s">
+      <c r="C24" s="112" t="s">
         <v>76</v>
       </c>
-      <c r="D24" s="112" t="s">
+      <c r="D24" s="113" t="s">
         <v>490</v>
       </c>
-      <c r="E24" s="112" t="s">
+      <c r="E24" s="113" t="s">
         <v>491</v>
       </c>
-      <c r="F24" s="40"/>
-      <c r="G24" s="41"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="42"/>
       <c r="H24" s="28"/>
       <c r="I24" s="29"/>
       <c r="J24" s="29"/>
@@ -12392,23 +12395,23 @@
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="74">
+      <c r="A25" s="75">
         <v>18.0</v>
       </c>
-      <c r="B25" s="110" t="s">
+      <c r="B25" s="111" t="s">
         <v>72</v>
       </c>
-      <c r="C25" s="111" t="s">
+      <c r="C25" s="112" t="s">
         <v>94</v>
       </c>
-      <c r="D25" s="112" t="s">
+      <c r="D25" s="113" t="s">
         <v>492</v>
       </c>
-      <c r="E25" s="112" t="s">
+      <c r="E25" s="113" t="s">
         <v>493</v>
       </c>
-      <c r="F25" s="40"/>
-      <c r="G25" s="41"/>
+      <c r="F25" s="41"/>
+      <c r="G25" s="42"/>
       <c r="H25" s="31"/>
       <c r="I25" s="32"/>
       <c r="J25" s="32"/>
@@ -12424,23 +12427,23 @@
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="74">
+      <c r="A26" s="75">
         <v>19.0</v>
       </c>
-      <c r="B26" s="110" t="s">
+      <c r="B26" s="111" t="s">
         <v>72</v>
       </c>
-      <c r="C26" s="111" t="s">
+      <c r="C26" s="112" t="s">
         <v>76</v>
       </c>
-      <c r="D26" s="112" t="s">
+      <c r="D26" s="113" t="s">
         <v>494</v>
       </c>
-      <c r="E26" s="112" t="s">
+      <c r="E26" s="113" t="s">
         <v>470</v>
       </c>
-      <c r="F26" s="40"/>
-      <c r="G26" s="41"/>
+      <c r="F26" s="41"/>
+      <c r="G26" s="42"/>
       <c r="H26" s="28"/>
       <c r="I26" s="29"/>
       <c r="J26" s="29"/>
@@ -12456,23 +12459,23 @@
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="74">
+      <c r="A27" s="75">
         <v>20.0</v>
       </c>
-      <c r="B27" s="110" t="s">
+      <c r="B27" s="111" t="s">
         <v>102</v>
       </c>
-      <c r="C27" s="111" t="s">
+      <c r="C27" s="112" t="s">
         <v>86</v>
       </c>
-      <c r="D27" s="112" t="s">
+      <c r="D27" s="113" t="s">
         <v>495</v>
       </c>
-      <c r="E27" s="112" t="s">
+      <c r="E27" s="113" t="s">
         <v>486</v>
       </c>
-      <c r="F27" s="40"/>
-      <c r="G27" s="41"/>
+      <c r="F27" s="41"/>
+      <c r="G27" s="42"/>
       <c r="H27" s="31"/>
       <c r="I27" s="32"/>
       <c r="J27" s="32"/>
@@ -12488,23 +12491,23 @@
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="74">
+      <c r="A28" s="75">
         <v>21.0</v>
       </c>
-      <c r="B28" s="110" t="s">
+      <c r="B28" s="111" t="s">
         <v>72</v>
       </c>
-      <c r="C28" s="111" t="s">
+      <c r="C28" s="112" t="s">
         <v>86</v>
       </c>
-      <c r="D28" s="112" t="s">
+      <c r="D28" s="113" t="s">
         <v>496</v>
       </c>
-      <c r="E28" s="112" t="s">
+      <c r="E28" s="113" t="s">
         <v>497</v>
       </c>
-      <c r="F28" s="40"/>
-      <c r="G28" s="41"/>
+      <c r="F28" s="41"/>
+      <c r="G28" s="42"/>
       <c r="H28" s="28"/>
       <c r="I28" s="29"/>
       <c r="J28" s="29"/>
@@ -12520,23 +12523,23 @@
       </c>
     </row>
     <row r="29" ht="17.25" customHeight="1">
-      <c r="A29" s="74">
+      <c r="A29" s="75">
         <v>22.0</v>
       </c>
-      <c r="B29" s="110" t="s">
+      <c r="B29" s="111" t="s">
         <v>72</v>
       </c>
-      <c r="C29" s="111" t="s">
+      <c r="C29" s="112" t="s">
         <v>94</v>
       </c>
-      <c r="D29" s="112" t="s">
+      <c r="D29" s="113" t="s">
         <v>498</v>
       </c>
-      <c r="E29" s="112" t="s">
+      <c r="E29" s="113" t="s">
         <v>181</v>
       </c>
-      <c r="F29" s="40"/>
-      <c r="G29" s="41"/>
+      <c r="F29" s="41"/>
+      <c r="G29" s="42"/>
       <c r="H29" s="31"/>
       <c r="I29" s="32"/>
       <c r="J29" s="32"/>
@@ -12552,23 +12555,23 @@
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="74">
+      <c r="A30" s="75">
         <v>23.0</v>
       </c>
-      <c r="B30" s="110" t="s">
+      <c r="B30" s="111" t="s">
         <v>67</v>
       </c>
-      <c r="C30" s="111" t="s">
+      <c r="C30" s="112" t="s">
         <v>76</v>
       </c>
-      <c r="D30" s="112" t="s">
+      <c r="D30" s="113" t="s">
         <v>499</v>
       </c>
-      <c r="E30" s="112" t="s">
+      <c r="E30" s="113" t="s">
         <v>500</v>
       </c>
-      <c r="F30" s="40"/>
-      <c r="G30" s="41"/>
+      <c r="F30" s="41"/>
+      <c r="G30" s="42"/>
       <c r="H30" s="28"/>
       <c r="I30" s="29"/>
       <c r="J30" s="29"/>
@@ -12584,23 +12587,23 @@
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="76">
+      <c r="A31" s="77">
         <v>24.0</v>
       </c>
-      <c r="B31" s="110" t="s">
+      <c r="B31" s="111" t="s">
         <v>67</v>
       </c>
-      <c r="C31" s="111" t="s">
+      <c r="C31" s="112" t="s">
         <v>76</v>
       </c>
-      <c r="D31" s="112" t="s">
+      <c r="D31" s="113" t="s">
         <v>282</v>
       </c>
-      <c r="E31" s="112" t="s">
+      <c r="E31" s="113" t="s">
         <v>501</v>
       </c>
-      <c r="F31" s="40"/>
-      <c r="G31" s="41"/>
+      <c r="F31" s="41"/>
+      <c r="G31" s="42"/>
       <c r="H31" s="31"/>
       <c r="I31" s="32"/>
       <c r="J31" s="32"/>
@@ -12616,23 +12619,23 @@
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="74">
+      <c r="A32" s="75">
         <v>25.0</v>
       </c>
-      <c r="B32" s="110" t="s">
+      <c r="B32" s="111" t="s">
         <v>67</v>
       </c>
-      <c r="C32" s="111" t="s">
+      <c r="C32" s="112" t="s">
         <v>86</v>
       </c>
-      <c r="D32" s="112" t="s">
+      <c r="D32" s="113" t="s">
         <v>502</v>
       </c>
-      <c r="E32" s="112" t="s">
+      <c r="E32" s="113" t="s">
         <v>503</v>
       </c>
-      <c r="F32" s="40"/>
-      <c r="G32" s="41"/>
+      <c r="F32" s="41"/>
+      <c r="G32" s="42"/>
       <c r="H32" s="28"/>
       <c r="I32" s="29"/>
       <c r="J32" s="29"/>
@@ -12648,23 +12651,23 @@
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="76">
+      <c r="A33" s="77">
         <v>26.0</v>
       </c>
-      <c r="B33" s="110" t="s">
+      <c r="B33" s="111" t="s">
         <v>67</v>
       </c>
-      <c r="C33" s="111" t="s">
+      <c r="C33" s="112" t="s">
         <v>76</v>
       </c>
-      <c r="D33" s="116" t="s">
+      <c r="D33" s="117" t="s">
         <v>181</v>
       </c>
-      <c r="E33" s="116" t="s">
+      <c r="E33" s="117" t="s">
         <v>504</v>
       </c>
-      <c r="F33" s="40"/>
-      <c r="G33" s="41"/>
+      <c r="F33" s="41"/>
+      <c r="G33" s="42"/>
       <c r="H33" s="31"/>
       <c r="I33" s="32"/>
       <c r="J33" s="32"/>
